--- a/Modelos/AP/FAURGS/plano_trabalho_FAURGS.xlsx
+++ b/Modelos/AP/FAURGS/plano_trabalho_FAURGS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pccli\OneDrive\Área de Trabalho\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA74B0A3-598B-470C-9656-24AA64761016}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFACF2D9-286F-4CB8-81B5-4AEC0B27C82F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11805" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2193,7 +2193,7 @@
     <t>Plano de Trabalho - FAURGS</t>
   </si>
   <si>
-    <t>2.5 - RESUMO</t>
+    <t>2.5 - Experiência da UFSM para executar o projeto e capacidade operacional (Citar brevemente experiência em projetos e infraestrutura disponível para desenvolver o projeto)</t>
   </si>
 </sst>
 </file>
@@ -4164,6 +4164,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="87" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4251,7 +4259,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="90" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4448,13 +4455,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="87" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6398,20 +6398,20 @@
       <c r="Z55" s="1"/>
     </row>
     <row r="56" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A56" s="300" t="s">
+      <c r="A56" s="190" t="s">
         <v>380</v>
       </c>
-      <c r="B56" s="301"/>
-      <c r="C56" s="301"/>
-      <c r="D56" s="301"/>
-      <c r="E56" s="301"/>
-      <c r="F56" s="301"/>
-      <c r="G56" s="301"/>
-      <c r="H56" s="301"/>
-      <c r="I56" s="301"/>
-      <c r="J56" s="301"/>
-      <c r="K56" s="301"/>
-      <c r="L56" s="227"/>
+      <c r="B56" s="191"/>
+      <c r="C56" s="191"/>
+      <c r="D56" s="191"/>
+      <c r="E56" s="191"/>
+      <c r="F56" s="191"/>
+      <c r="G56" s="191"/>
+      <c r="H56" s="191"/>
+      <c r="I56" s="191"/>
+      <c r="J56" s="191"/>
+      <c r="K56" s="191"/>
+      <c r="L56" s="192"/>
       <c r="M56" s="1"/>
       <c r="N56" s="1"/>
       <c r="O56" s="1"/>
@@ -6428,18 +6428,18 @@
       <c r="Z56" s="1"/>
     </row>
     <row r="57" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A57" s="302"/>
-      <c r="B57" s="303"/>
-      <c r="C57" s="303"/>
-      <c r="D57" s="303"/>
-      <c r="E57" s="303"/>
-      <c r="F57" s="303"/>
-      <c r="G57" s="303"/>
-      <c r="H57" s="303"/>
-      <c r="I57" s="303"/>
-      <c r="J57" s="303"/>
-      <c r="K57" s="303"/>
-      <c r="L57" s="304"/>
+      <c r="A57" s="193"/>
+      <c r="B57" s="194"/>
+      <c r="C57" s="194"/>
+      <c r="D57" s="194"/>
+      <c r="E57" s="194"/>
+      <c r="F57" s="194"/>
+      <c r="G57" s="194"/>
+      <c r="H57" s="194"/>
+      <c r="I57" s="194"/>
+      <c r="J57" s="194"/>
+      <c r="K57" s="194"/>
+      <c r="L57" s="195"/>
       <c r="M57" s="1"/>
       <c r="N57" s="1"/>
       <c r="O57" s="1"/>
@@ -6456,7 +6456,7 @@
       <c r="Z57" s="1"/>
     </row>
     <row r="58" spans="1:26" ht="144" customHeight="1">
-      <c r="A58" s="190" t="s">
+      <c r="A58" s="196" t="s">
         <v>51</v>
       </c>
       <c r="B58" s="117"/>
@@ -6514,7 +6514,7 @@
       <c r="Z59" s="1"/>
     </row>
     <row r="60" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A60" s="191" t="s">
+      <c r="A60" s="197" t="s">
         <v>52</v>
       </c>
       <c r="B60" s="117"/>
@@ -6544,7 +6544,7 @@
       <c r="Z60" s="1"/>
     </row>
     <row r="61" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A61" s="192" t="s">
+      <c r="A61" s="198" t="s">
         <v>53</v>
       </c>
       <c r="B61" s="131"/>
@@ -6602,7 +6602,7 @@
       <c r="Z62" s="1"/>
     </row>
     <row r="63" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A63" s="205" t="s">
+      <c r="A63" s="211" t="s">
         <v>54</v>
       </c>
       <c r="B63" s="87"/>
@@ -6635,7 +6635,7 @@
     </row>
     <row r="64" spans="1:26" ht="18" customHeight="1">
       <c r="A64" s="12"/>
-      <c r="B64" s="206" t="s">
+      <c r="B64" s="212" t="s">
         <v>56</v>
       </c>
       <c r="C64" s="103"/>
@@ -6650,7 +6650,7 @@
         <f>K97</f>
         <v>0</v>
       </c>
-      <c r="L64" s="197"/>
+      <c r="L64" s="203"/>
       <c r="M64" s="1"/>
       <c r="N64" s="1"/>
       <c r="O64" s="1"/>
@@ -6668,7 +6668,7 @@
     </row>
     <row r="65" spans="1:26" ht="18.75" customHeight="1">
       <c r="A65" s="13"/>
-      <c r="B65" s="207"/>
+      <c r="B65" s="213"/>
       <c r="C65" s="97"/>
       <c r="D65" s="97"/>
       <c r="E65" s="97"/>
@@ -6677,8 +6677,8 @@
       <c r="H65" s="97"/>
       <c r="I65" s="97"/>
       <c r="J65" s="101"/>
-      <c r="K65" s="198"/>
-      <c r="L65" s="199"/>
+      <c r="K65" s="204"/>
+      <c r="L65" s="205"/>
       <c r="M65" s="1"/>
       <c r="N65" s="1"/>
       <c r="O65" s="1"/>
@@ -6696,7 +6696,7 @@
     </row>
     <row r="66" spans="1:26" ht="18.75" customHeight="1">
       <c r="A66" s="13"/>
-      <c r="B66" s="208" t="s">
+      <c r="B66" s="214" t="s">
         <v>57</v>
       </c>
       <c r="C66" s="103"/>
@@ -6707,8 +6707,8 @@
       <c r="H66" s="103"/>
       <c r="I66" s="103"/>
       <c r="J66" s="100"/>
-      <c r="K66" s="198"/>
-      <c r="L66" s="199"/>
+      <c r="K66" s="204"/>
+      <c r="L66" s="205"/>
       <c r="M66" s="1"/>
       <c r="N66" s="1"/>
       <c r="O66" s="1"/>
@@ -6726,7 +6726,7 @@
     </row>
     <row r="67" spans="1:26" ht="25.5" customHeight="1">
       <c r="A67" s="14"/>
-      <c r="B67" s="207"/>
+      <c r="B67" s="213"/>
       <c r="C67" s="97"/>
       <c r="D67" s="97"/>
       <c r="E67" s="97"/>
@@ -6735,8 +6735,8 @@
       <c r="H67" s="97"/>
       <c r="I67" s="97"/>
       <c r="J67" s="101"/>
-      <c r="K67" s="198"/>
-      <c r="L67" s="199"/>
+      <c r="K67" s="204"/>
+      <c r="L67" s="205"/>
       <c r="M67" s="1"/>
       <c r="N67" s="1"/>
       <c r="O67" s="1"/>
@@ -6753,8 +6753,8 @@
       <c r="Z67" s="1"/>
     </row>
     <row r="68" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A68" s="195"/>
-      <c r="B68" s="196" t="s">
+      <c r="A68" s="201"/>
+      <c r="B68" s="202" t="s">
         <v>58</v>
       </c>
       <c r="C68" s="103"/>
@@ -6765,8 +6765,8 @@
       <c r="H68" s="103"/>
       <c r="I68" s="103"/>
       <c r="J68" s="100"/>
-      <c r="K68" s="198"/>
-      <c r="L68" s="199"/>
+      <c r="K68" s="204"/>
+      <c r="L68" s="205"/>
       <c r="M68" s="1"/>
       <c r="N68" s="1"/>
       <c r="O68" s="1"/>
@@ -6783,7 +6783,7 @@
       <c r="Z68" s="1"/>
     </row>
     <row r="69" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A69" s="194"/>
+      <c r="A69" s="200"/>
       <c r="B69" s="105"/>
       <c r="C69" s="97"/>
       <c r="D69" s="97"/>
@@ -6793,8 +6793,8 @@
       <c r="H69" s="97"/>
       <c r="I69" s="97"/>
       <c r="J69" s="101"/>
-      <c r="K69" s="198"/>
-      <c r="L69" s="199"/>
+      <c r="K69" s="204"/>
+      <c r="L69" s="205"/>
       <c r="M69" s="1"/>
       <c r="N69" s="1"/>
       <c r="O69" s="1"/>
@@ -6811,8 +6811,8 @@
       <c r="Z69" s="1"/>
     </row>
     <row r="70" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A70" s="193"/>
-      <c r="B70" s="196" t="s">
+      <c r="A70" s="199"/>
+      <c r="B70" s="202" t="s">
         <v>59</v>
       </c>
       <c r="C70" s="103"/>
@@ -6823,8 +6823,8 @@
       <c r="H70" s="103"/>
       <c r="I70" s="103"/>
       <c r="J70" s="100"/>
-      <c r="K70" s="198"/>
-      <c r="L70" s="199"/>
+      <c r="K70" s="204"/>
+      <c r="L70" s="205"/>
       <c r="M70" s="1"/>
       <c r="N70" s="1"/>
       <c r="O70" s="1"/>
@@ -6841,7 +6841,7 @@
       <c r="Z70" s="1"/>
     </row>
     <row r="71" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A71" s="194"/>
+      <c r="A71" s="200"/>
       <c r="B71" s="105"/>
       <c r="C71" s="97"/>
       <c r="D71" s="97"/>
@@ -6851,8 +6851,8 @@
       <c r="H71" s="97"/>
       <c r="I71" s="97"/>
       <c r="J71" s="101"/>
-      <c r="K71" s="198"/>
-      <c r="L71" s="199"/>
+      <c r="K71" s="204"/>
+      <c r="L71" s="205"/>
       <c r="M71" s="1"/>
       <c r="N71" s="1"/>
       <c r="O71" s="1"/>
@@ -6869,8 +6869,8 @@
       <c r="Z71" s="1"/>
     </row>
     <row r="72" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A72" s="193"/>
-      <c r="B72" s="209" t="s">
+      <c r="A72" s="199"/>
+      <c r="B72" s="215" t="s">
         <v>60</v>
       </c>
       <c r="C72" s="103"/>
@@ -6881,8 +6881,8 @@
       <c r="H72" s="103"/>
       <c r="I72" s="103"/>
       <c r="J72" s="100"/>
-      <c r="K72" s="198"/>
-      <c r="L72" s="199"/>
+      <c r="K72" s="204"/>
+      <c r="L72" s="205"/>
       <c r="M72" s="1"/>
       <c r="N72" s="1"/>
       <c r="O72" s="1"/>
@@ -6899,7 +6899,7 @@
       <c r="Z72" s="1"/>
     </row>
     <row r="73" spans="1:26" ht="23.25" customHeight="1">
-      <c r="A73" s="194"/>
+      <c r="A73" s="200"/>
       <c r="B73" s="105"/>
       <c r="C73" s="97"/>
       <c r="D73" s="97"/>
@@ -6909,8 +6909,8 @@
       <c r="H73" s="97"/>
       <c r="I73" s="97"/>
       <c r="J73" s="101"/>
-      <c r="K73" s="198"/>
-      <c r="L73" s="199"/>
+      <c r="K73" s="204"/>
+      <c r="L73" s="205"/>
       <c r="M73" s="1"/>
       <c r="N73" s="1"/>
       <c r="O73" s="1"/>
@@ -6927,8 +6927,8 @@
       <c r="Z73" s="1"/>
     </row>
     <row r="74" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A74" s="193"/>
-      <c r="B74" s="196" t="s">
+      <c r="A74" s="199"/>
+      <c r="B74" s="202" t="s">
         <v>61</v>
       </c>
       <c r="C74" s="103"/>
@@ -6939,8 +6939,8 @@
       <c r="H74" s="103"/>
       <c r="I74" s="103"/>
       <c r="J74" s="100"/>
-      <c r="K74" s="198"/>
-      <c r="L74" s="199"/>
+      <c r="K74" s="204"/>
+      <c r="L74" s="205"/>
       <c r="M74" s="1"/>
       <c r="N74" s="1"/>
       <c r="O74" s="1"/>
@@ -6957,7 +6957,7 @@
       <c r="Z74" s="1"/>
     </row>
     <row r="75" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A75" s="194"/>
+      <c r="A75" s="200"/>
       <c r="B75" s="105"/>
       <c r="C75" s="97"/>
       <c r="D75" s="97"/>
@@ -6967,8 +6967,8 @@
       <c r="H75" s="97"/>
       <c r="I75" s="97"/>
       <c r="J75" s="101"/>
-      <c r="K75" s="198"/>
-      <c r="L75" s="199"/>
+      <c r="K75" s="204"/>
+      <c r="L75" s="205"/>
       <c r="M75" s="1"/>
       <c r="N75" s="1"/>
       <c r="O75" s="1"/>
@@ -6985,8 +6985,8 @@
       <c r="Z75" s="1"/>
     </row>
     <row r="76" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A76" s="193"/>
-      <c r="B76" s="196" t="s">
+      <c r="A76" s="199"/>
+      <c r="B76" s="202" t="s">
         <v>62</v>
       </c>
       <c r="C76" s="103"/>
@@ -6997,8 +6997,8 @@
       <c r="H76" s="103"/>
       <c r="I76" s="103"/>
       <c r="J76" s="100"/>
-      <c r="K76" s="198"/>
-      <c r="L76" s="199"/>
+      <c r="K76" s="204"/>
+      <c r="L76" s="205"/>
       <c r="M76" s="1"/>
       <c r="N76" s="1"/>
       <c r="O76" s="1"/>
@@ -7015,7 +7015,7 @@
       <c r="Z76" s="1"/>
     </row>
     <row r="77" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A77" s="194"/>
+      <c r="A77" s="200"/>
       <c r="B77" s="105"/>
       <c r="C77" s="97"/>
       <c r="D77" s="97"/>
@@ -7025,8 +7025,8 @@
       <c r="H77" s="97"/>
       <c r="I77" s="97"/>
       <c r="J77" s="101"/>
-      <c r="K77" s="198"/>
-      <c r="L77" s="199"/>
+      <c r="K77" s="204"/>
+      <c r="L77" s="205"/>
       <c r="M77" s="1"/>
       <c r="N77" s="1"/>
       <c r="O77" s="1"/>
@@ -7043,8 +7043,8 @@
       <c r="Z77" s="1"/>
     </row>
     <row r="78" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A78" s="193"/>
-      <c r="B78" s="196" t="s">
+      <c r="A78" s="199"/>
+      <c r="B78" s="202" t="s">
         <v>63</v>
       </c>
       <c r="C78" s="103"/>
@@ -7055,8 +7055,8 @@
       <c r="H78" s="103"/>
       <c r="I78" s="103"/>
       <c r="J78" s="100"/>
-      <c r="K78" s="198"/>
-      <c r="L78" s="199"/>
+      <c r="K78" s="204"/>
+      <c r="L78" s="205"/>
       <c r="M78" s="1"/>
       <c r="N78" s="1"/>
       <c r="O78" s="1"/>
@@ -7073,7 +7073,7 @@
       <c r="Z78" s="1"/>
     </row>
     <row r="79" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A79" s="194"/>
+      <c r="A79" s="200"/>
       <c r="B79" s="105"/>
       <c r="C79" s="97"/>
       <c r="D79" s="97"/>
@@ -7083,8 +7083,8 @@
       <c r="H79" s="97"/>
       <c r="I79" s="97"/>
       <c r="J79" s="101"/>
-      <c r="K79" s="198"/>
-      <c r="L79" s="199"/>
+      <c r="K79" s="204"/>
+      <c r="L79" s="205"/>
       <c r="M79" s="1"/>
       <c r="N79" s="1"/>
       <c r="O79" s="1"/>
@@ -7101,8 +7101,8 @@
       <c r="Z79" s="1"/>
     </row>
     <row r="80" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A80" s="193"/>
-      <c r="B80" s="196" t="s">
+      <c r="A80" s="199"/>
+      <c r="B80" s="202" t="s">
         <v>64</v>
       </c>
       <c r="C80" s="103"/>
@@ -7113,8 +7113,8 @@
       <c r="H80" s="103"/>
       <c r="I80" s="103"/>
       <c r="J80" s="100"/>
-      <c r="K80" s="198"/>
-      <c r="L80" s="199"/>
+      <c r="K80" s="204"/>
+      <c r="L80" s="205"/>
       <c r="M80" s="1"/>
       <c r="N80" s="1"/>
       <c r="O80" s="1"/>
@@ -7131,7 +7131,7 @@
       <c r="Z80" s="1"/>
     </row>
     <row r="81" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A81" s="194"/>
+      <c r="A81" s="200"/>
       <c r="B81" s="105"/>
       <c r="C81" s="97"/>
       <c r="D81" s="97"/>
@@ -7141,8 +7141,8 @@
       <c r="H81" s="97"/>
       <c r="I81" s="97"/>
       <c r="J81" s="101"/>
-      <c r="K81" s="198"/>
-      <c r="L81" s="199"/>
+      <c r="K81" s="204"/>
+      <c r="L81" s="205"/>
       <c r="M81" s="1"/>
       <c r="N81" s="1"/>
       <c r="O81" s="1"/>
@@ -7159,8 +7159,8 @@
       <c r="Z81" s="1"/>
     </row>
     <row r="82" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A82" s="193"/>
-      <c r="B82" s="202" t="s">
+      <c r="A82" s="199"/>
+      <c r="B82" s="208" t="s">
         <v>65</v>
       </c>
       <c r="C82" s="111"/>
@@ -7171,8 +7171,8 @@
       <c r="H82" s="111"/>
       <c r="I82" s="111"/>
       <c r="J82" s="135"/>
-      <c r="K82" s="198"/>
-      <c r="L82" s="199"/>
+      <c r="K82" s="204"/>
+      <c r="L82" s="205"/>
       <c r="M82" s="1"/>
       <c r="N82" s="1"/>
       <c r="O82" s="1"/>
@@ -7189,18 +7189,18 @@
       <c r="Z82" s="1"/>
     </row>
     <row r="83" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A83" s="194"/>
-      <c r="B83" s="200"/>
-      <c r="C83" s="203"/>
-      <c r="D83" s="203"/>
-      <c r="E83" s="203"/>
-      <c r="F83" s="203"/>
-      <c r="G83" s="203"/>
-      <c r="H83" s="203"/>
-      <c r="I83" s="203"/>
-      <c r="J83" s="204"/>
-      <c r="K83" s="200"/>
-      <c r="L83" s="201"/>
+      <c r="A83" s="200"/>
+      <c r="B83" s="206"/>
+      <c r="C83" s="209"/>
+      <c r="D83" s="209"/>
+      <c r="E83" s="209"/>
+      <c r="F83" s="209"/>
+      <c r="G83" s="209"/>
+      <c r="H83" s="209"/>
+      <c r="I83" s="209"/>
+      <c r="J83" s="210"/>
+      <c r="K83" s="206"/>
+      <c r="L83" s="207"/>
       <c r="M83" s="1"/>
       <c r="N83" s="1"/>
       <c r="O83" s="1"/>
@@ -8120,13 +8120,13 @@
       <c r="Z113" s="19"/>
     </row>
     <row r="114" spans="1:26" ht="24.75" customHeight="1">
-      <c r="A114" s="210"/>
+      <c r="A114" s="216"/>
       <c r="B114" s="177"/>
-      <c r="C114" s="211"/>
+      <c r="C114" s="217"/>
       <c r="D114" s="114"/>
-      <c r="E114" s="212"/>
-      <c r="F114" s="213"/>
-      <c r="G114" s="212"/>
+      <c r="E114" s="218"/>
+      <c r="F114" s="219"/>
+      <c r="G114" s="218"/>
       <c r="H114" s="20"/>
       <c r="I114" s="21"/>
       <c r="J114" s="22"/>
@@ -8151,12 +8151,12 @@
       <c r="Z114" s="19"/>
     </row>
     <row r="115" spans="1:26" ht="24.75" customHeight="1">
-      <c r="A115" s="210"/>
+      <c r="A115" s="216"/>
       <c r="B115" s="177"/>
-      <c r="C115" s="214"/>
+      <c r="C115" s="220"/>
       <c r="D115" s="87"/>
       <c r="E115" s="91"/>
-      <c r="F115" s="215"/>
+      <c r="F115" s="221"/>
       <c r="G115" s="91"/>
       <c r="H115" s="25"/>
       <c r="I115" s="26"/>
@@ -8182,12 +8182,12 @@
       <c r="Z115" s="19"/>
     </row>
     <row r="116" spans="1:26" ht="24.75" customHeight="1">
-      <c r="A116" s="210"/>
+      <c r="A116" s="216"/>
       <c r="B116" s="177"/>
-      <c r="C116" s="214"/>
+      <c r="C116" s="220"/>
       <c r="D116" s="87"/>
       <c r="E116" s="91"/>
-      <c r="F116" s="215"/>
+      <c r="F116" s="221"/>
       <c r="G116" s="91"/>
       <c r="H116" s="25"/>
       <c r="I116" s="26"/>
@@ -8213,12 +8213,12 @@
       <c r="Z116" s="19"/>
     </row>
     <row r="117" spans="1:26" ht="24.75" customHeight="1">
-      <c r="A117" s="210"/>
+      <c r="A117" s="216"/>
       <c r="B117" s="177"/>
-      <c r="C117" s="214"/>
+      <c r="C117" s="220"/>
       <c r="D117" s="87"/>
       <c r="E117" s="91"/>
-      <c r="F117" s="215"/>
+      <c r="F117" s="221"/>
       <c r="G117" s="91"/>
       <c r="H117" s="25"/>
       <c r="I117" s="26"/>
@@ -8244,12 +8244,12 @@
       <c r="Z117" s="19"/>
     </row>
     <row r="118" spans="1:26" ht="24.75" customHeight="1">
-      <c r="A118" s="210"/>
+      <c r="A118" s="216"/>
       <c r="B118" s="177"/>
-      <c r="C118" s="214"/>
+      <c r="C118" s="220"/>
       <c r="D118" s="87"/>
       <c r="E118" s="91"/>
-      <c r="F118" s="215"/>
+      <c r="F118" s="221"/>
       <c r="G118" s="91"/>
       <c r="H118" s="28"/>
       <c r="I118" s="26"/>
@@ -8275,12 +8275,12 @@
       <c r="Z118" s="19"/>
     </row>
     <row r="119" spans="1:26" ht="24.75" customHeight="1">
-      <c r="A119" s="210"/>
+      <c r="A119" s="216"/>
       <c r="B119" s="177"/>
-      <c r="C119" s="214"/>
+      <c r="C119" s="220"/>
       <c r="D119" s="87"/>
       <c r="E119" s="91"/>
-      <c r="F119" s="217"/>
+      <c r="F119" s="223"/>
       <c r="G119" s="91"/>
       <c r="H119" s="28"/>
       <c r="I119" s="26"/>
@@ -8306,12 +8306,12 @@
       <c r="Z119" s="19"/>
     </row>
     <row r="120" spans="1:26" ht="24.75" customHeight="1">
-      <c r="A120" s="210"/>
+      <c r="A120" s="216"/>
       <c r="B120" s="177"/>
-      <c r="C120" s="214"/>
+      <c r="C120" s="220"/>
       <c r="D120" s="87"/>
       <c r="E120" s="91"/>
-      <c r="F120" s="217"/>
+      <c r="F120" s="223"/>
       <c r="G120" s="91"/>
       <c r="H120" s="28"/>
       <c r="I120" s="26"/>
@@ -8337,12 +8337,12 @@
       <c r="Z120" s="19"/>
     </row>
     <row r="121" spans="1:26" ht="24.75" customHeight="1">
-      <c r="A121" s="210"/>
+      <c r="A121" s="216"/>
       <c r="B121" s="177"/>
-      <c r="C121" s="214"/>
+      <c r="C121" s="220"/>
       <c r="D121" s="87"/>
       <c r="E121" s="91"/>
-      <c r="F121" s="217"/>
+      <c r="F121" s="223"/>
       <c r="G121" s="91"/>
       <c r="H121" s="28"/>
       <c r="I121" s="26"/>
@@ -8368,12 +8368,12 @@
       <c r="Z121" s="19"/>
     </row>
     <row r="122" spans="1:26" ht="24.75" customHeight="1">
-      <c r="A122" s="210"/>
+      <c r="A122" s="216"/>
       <c r="B122" s="177"/>
-      <c r="C122" s="214"/>
+      <c r="C122" s="220"/>
       <c r="D122" s="87"/>
       <c r="E122" s="91"/>
-      <c r="F122" s="217"/>
+      <c r="F122" s="223"/>
       <c r="G122" s="91"/>
       <c r="H122" s="28"/>
       <c r="I122" s="26"/>
@@ -8399,12 +8399,12 @@
       <c r="Z122" s="19"/>
     </row>
     <row r="123" spans="1:26" ht="24.75" customHeight="1">
-      <c r="A123" s="210"/>
+      <c r="A123" s="216"/>
       <c r="B123" s="177"/>
-      <c r="C123" s="214"/>
+      <c r="C123" s="220"/>
       <c r="D123" s="87"/>
       <c r="E123" s="91"/>
-      <c r="F123" s="217"/>
+      <c r="F123" s="223"/>
       <c r="G123" s="91"/>
       <c r="H123" s="28"/>
       <c r="I123" s="26"/>
@@ -8430,12 +8430,12 @@
       <c r="Z123" s="19"/>
     </row>
     <row r="124" spans="1:26" ht="24.75" customHeight="1">
-      <c r="A124" s="210"/>
+      <c r="A124" s="216"/>
       <c r="B124" s="177"/>
-      <c r="C124" s="216"/>
+      <c r="C124" s="222"/>
       <c r="D124" s="87"/>
       <c r="E124" s="91"/>
-      <c r="F124" s="217"/>
+      <c r="F124" s="223"/>
       <c r="G124" s="91"/>
       <c r="H124" s="28"/>
       <c r="I124" s="26"/>
@@ -8461,12 +8461,12 @@
       <c r="Z124" s="19"/>
     </row>
     <row r="125" spans="1:26" ht="24.75" customHeight="1">
-      <c r="A125" s="210"/>
+      <c r="A125" s="216"/>
       <c r="B125" s="177"/>
-      <c r="C125" s="216"/>
+      <c r="C125" s="222"/>
       <c r="D125" s="87"/>
       <c r="E125" s="91"/>
-      <c r="F125" s="217"/>
+      <c r="F125" s="223"/>
       <c r="G125" s="91"/>
       <c r="H125" s="28"/>
       <c r="I125" s="26"/>
@@ -8492,12 +8492,12 @@
       <c r="Z125" s="19"/>
     </row>
     <row r="126" spans="1:26" ht="24.75" customHeight="1">
-      <c r="A126" s="210"/>
+      <c r="A126" s="216"/>
       <c r="B126" s="177"/>
-      <c r="C126" s="216"/>
+      <c r="C126" s="222"/>
       <c r="D126" s="87"/>
       <c r="E126" s="91"/>
-      <c r="F126" s="217"/>
+      <c r="F126" s="223"/>
       <c r="G126" s="91"/>
       <c r="H126" s="28"/>
       <c r="I126" s="26"/>
@@ -8523,12 +8523,12 @@
       <c r="Z126" s="19"/>
     </row>
     <row r="127" spans="1:26" ht="24.75" customHeight="1">
-      <c r="A127" s="210"/>
+      <c r="A127" s="216"/>
       <c r="B127" s="177"/>
-      <c r="C127" s="216"/>
+      <c r="C127" s="222"/>
       <c r="D127" s="87"/>
       <c r="E127" s="91"/>
-      <c r="F127" s="217"/>
+      <c r="F127" s="223"/>
       <c r="G127" s="91"/>
       <c r="H127" s="28"/>
       <c r="I127" s="26"/>
@@ -8554,12 +8554,12 @@
       <c r="Z127" s="19"/>
     </row>
     <row r="128" spans="1:26" ht="24.75" customHeight="1">
-      <c r="A128" s="210"/>
+      <c r="A128" s="216"/>
       <c r="B128" s="177"/>
-      <c r="C128" s="216"/>
+      <c r="C128" s="222"/>
       <c r="D128" s="87"/>
       <c r="E128" s="91"/>
-      <c r="F128" s="217"/>
+      <c r="F128" s="223"/>
       <c r="G128" s="91"/>
       <c r="H128" s="28"/>
       <c r="I128" s="26"/>
@@ -8585,12 +8585,12 @@
       <c r="Z128" s="19"/>
     </row>
     <row r="129" spans="1:26" ht="24.75" customHeight="1">
-      <c r="A129" s="210"/>
+      <c r="A129" s="216"/>
       <c r="B129" s="177"/>
-      <c r="C129" s="216"/>
+      <c r="C129" s="222"/>
       <c r="D129" s="87"/>
       <c r="E129" s="91"/>
-      <c r="F129" s="217"/>
+      <c r="F129" s="223"/>
       <c r="G129" s="91"/>
       <c r="H129" s="28"/>
       <c r="I129" s="26"/>
@@ -8616,12 +8616,12 @@
       <c r="Z129" s="19"/>
     </row>
     <row r="130" spans="1:26" ht="24.75" customHeight="1">
-      <c r="A130" s="210"/>
+      <c r="A130" s="216"/>
       <c r="B130" s="177"/>
-      <c r="C130" s="216"/>
+      <c r="C130" s="222"/>
       <c r="D130" s="87"/>
       <c r="E130" s="91"/>
-      <c r="F130" s="217"/>
+      <c r="F130" s="223"/>
       <c r="G130" s="91"/>
       <c r="H130" s="28"/>
       <c r="I130" s="26"/>
@@ -8647,12 +8647,12 @@
       <c r="Z130" s="19"/>
     </row>
     <row r="131" spans="1:26" ht="24.75" customHeight="1">
-      <c r="A131" s="210"/>
+      <c r="A131" s="216"/>
       <c r="B131" s="177"/>
-      <c r="C131" s="216"/>
+      <c r="C131" s="222"/>
       <c r="D131" s="87"/>
       <c r="E131" s="91"/>
-      <c r="F131" s="217"/>
+      <c r="F131" s="223"/>
       <c r="G131" s="91"/>
       <c r="H131" s="28"/>
       <c r="I131" s="26"/>
@@ -8678,12 +8678,12 @@
       <c r="Z131" s="19"/>
     </row>
     <row r="132" spans="1:26" ht="24.75" customHeight="1">
-      <c r="A132" s="210"/>
+      <c r="A132" s="216"/>
       <c r="B132" s="177"/>
-      <c r="C132" s="216"/>
+      <c r="C132" s="222"/>
       <c r="D132" s="87"/>
       <c r="E132" s="91"/>
-      <c r="F132" s="217"/>
+      <c r="F132" s="223"/>
       <c r="G132" s="91"/>
       <c r="H132" s="28"/>
       <c r="I132" s="26"/>
@@ -8709,12 +8709,12 @@
       <c r="Z132" s="19"/>
     </row>
     <row r="133" spans="1:26" ht="24.75" customHeight="1">
-      <c r="A133" s="210"/>
+      <c r="A133" s="216"/>
       <c r="B133" s="177"/>
-      <c r="C133" s="216"/>
+      <c r="C133" s="222"/>
       <c r="D133" s="87"/>
       <c r="E133" s="91"/>
-      <c r="F133" s="217"/>
+      <c r="F133" s="223"/>
       <c r="G133" s="91"/>
       <c r="H133" s="28"/>
       <c r="I133" s="26"/>
@@ -8740,12 +8740,12 @@
       <c r="Z133" s="19"/>
     </row>
     <row r="134" spans="1:26" ht="24.75" customHeight="1">
-      <c r="A134" s="210"/>
+      <c r="A134" s="216"/>
       <c r="B134" s="177"/>
-      <c r="C134" s="216"/>
+      <c r="C134" s="222"/>
       <c r="D134" s="87"/>
       <c r="E134" s="91"/>
-      <c r="F134" s="217"/>
+      <c r="F134" s="223"/>
       <c r="G134" s="91"/>
       <c r="H134" s="28"/>
       <c r="I134" s="26"/>
@@ -8771,12 +8771,12 @@
       <c r="Z134" s="19"/>
     </row>
     <row r="135" spans="1:26" ht="24.75" customHeight="1">
-      <c r="A135" s="210"/>
+      <c r="A135" s="216"/>
       <c r="B135" s="177"/>
-      <c r="C135" s="216"/>
+      <c r="C135" s="222"/>
       <c r="D135" s="87"/>
       <c r="E135" s="91"/>
-      <c r="F135" s="217"/>
+      <c r="F135" s="223"/>
       <c r="G135" s="91"/>
       <c r="H135" s="28"/>
       <c r="I135" s="26"/>
@@ -8802,12 +8802,12 @@
       <c r="Z135" s="19"/>
     </row>
     <row r="136" spans="1:26" ht="24.75" customHeight="1">
-      <c r="A136" s="210"/>
+      <c r="A136" s="216"/>
       <c r="B136" s="177"/>
-      <c r="C136" s="216"/>
+      <c r="C136" s="222"/>
       <c r="D136" s="87"/>
       <c r="E136" s="91"/>
-      <c r="F136" s="217"/>
+      <c r="F136" s="223"/>
       <c r="G136" s="91"/>
       <c r="H136" s="28"/>
       <c r="I136" s="26"/>
@@ -8833,12 +8833,12 @@
       <c r="Z136" s="19"/>
     </row>
     <row r="137" spans="1:26" ht="24.75" customHeight="1">
-      <c r="A137" s="210"/>
+      <c r="A137" s="216"/>
       <c r="B137" s="177"/>
-      <c r="C137" s="216"/>
+      <c r="C137" s="222"/>
       <c r="D137" s="87"/>
       <c r="E137" s="91"/>
-      <c r="F137" s="217"/>
+      <c r="F137" s="223"/>
       <c r="G137" s="91"/>
       <c r="H137" s="28"/>
       <c r="I137" s="26"/>
@@ -8864,12 +8864,12 @@
       <c r="Z137" s="19"/>
     </row>
     <row r="138" spans="1:26" ht="24.75" customHeight="1">
-      <c r="A138" s="210"/>
+      <c r="A138" s="216"/>
       <c r="B138" s="177"/>
-      <c r="C138" s="216"/>
+      <c r="C138" s="222"/>
       <c r="D138" s="87"/>
       <c r="E138" s="91"/>
-      <c r="F138" s="217"/>
+      <c r="F138" s="223"/>
       <c r="G138" s="91"/>
       <c r="H138" s="28"/>
       <c r="I138" s="26"/>
@@ -8895,12 +8895,12 @@
       <c r="Z138" s="19"/>
     </row>
     <row r="139" spans="1:26" ht="24.75" customHeight="1">
-      <c r="A139" s="210"/>
+      <c r="A139" s="216"/>
       <c r="B139" s="177"/>
-      <c r="C139" s="216"/>
+      <c r="C139" s="222"/>
       <c r="D139" s="87"/>
       <c r="E139" s="91"/>
-      <c r="F139" s="217"/>
+      <c r="F139" s="223"/>
       <c r="G139" s="91"/>
       <c r="H139" s="28"/>
       <c r="I139" s="26"/>
@@ -8926,12 +8926,12 @@
       <c r="Z139" s="19"/>
     </row>
     <row r="140" spans="1:26" ht="24.75" customHeight="1">
-      <c r="A140" s="210"/>
+      <c r="A140" s="216"/>
       <c r="B140" s="177"/>
-      <c r="C140" s="216"/>
+      <c r="C140" s="222"/>
       <c r="D140" s="87"/>
       <c r="E140" s="91"/>
-      <c r="F140" s="217"/>
+      <c r="F140" s="223"/>
       <c r="G140" s="91"/>
       <c r="H140" s="28"/>
       <c r="I140" s="26"/>
@@ -8957,12 +8957,12 @@
       <c r="Z140" s="19"/>
     </row>
     <row r="141" spans="1:26" ht="23.25" customHeight="1">
-      <c r="A141" s="210"/>
+      <c r="A141" s="216"/>
       <c r="B141" s="177"/>
-      <c r="C141" s="216"/>
+      <c r="C141" s="222"/>
       <c r="D141" s="87"/>
       <c r="E141" s="91"/>
-      <c r="F141" s="217"/>
+      <c r="F141" s="223"/>
       <c r="G141" s="91"/>
       <c r="H141" s="28"/>
       <c r="I141" s="26"/>
@@ -8988,12 +8988,12 @@
       <c r="Z141" s="1"/>
     </row>
     <row r="142" spans="1:26" ht="24" customHeight="1">
-      <c r="A142" s="210"/>
+      <c r="A142" s="216"/>
       <c r="B142" s="177"/>
-      <c r="C142" s="216"/>
+      <c r="C142" s="222"/>
       <c r="D142" s="87"/>
       <c r="E142" s="91"/>
-      <c r="F142" s="217"/>
+      <c r="F142" s="223"/>
       <c r="G142" s="91"/>
       <c r="H142" s="28"/>
       <c r="I142" s="26"/>
@@ -9019,12 +9019,12 @@
       <c r="Z142" s="1"/>
     </row>
     <row r="143" spans="1:26" ht="21.75" customHeight="1">
-      <c r="A143" s="210"/>
+      <c r="A143" s="216"/>
       <c r="B143" s="177"/>
-      <c r="C143" s="216"/>
+      <c r="C143" s="222"/>
       <c r="D143" s="87"/>
       <c r="E143" s="91"/>
-      <c r="F143" s="217"/>
+      <c r="F143" s="223"/>
       <c r="G143" s="91"/>
       <c r="H143" s="28"/>
       <c r="I143" s="26"/>
@@ -9050,12 +9050,12 @@
       <c r="Z143" s="1"/>
     </row>
     <row r="144" spans="1:26" ht="24" customHeight="1">
-      <c r="A144" s="219"/>
+      <c r="A144" s="225"/>
       <c r="B144" s="91"/>
-      <c r="C144" s="220"/>
+      <c r="C144" s="226"/>
       <c r="D144" s="162"/>
       <c r="E144" s="158"/>
-      <c r="F144" s="221"/>
+      <c r="F144" s="227"/>
       <c r="G144" s="158"/>
       <c r="H144" s="30"/>
       <c r="I144" s="31"/>
@@ -9109,20 +9109,20 @@
       <c r="Z145" s="1"/>
     </row>
     <row r="146" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A146" s="225" t="s">
+      <c r="A146" s="231" t="s">
         <v>86</v>
       </c>
-      <c r="B146" s="226"/>
-      <c r="C146" s="226"/>
-      <c r="D146" s="226"/>
-      <c r="E146" s="226"/>
-      <c r="F146" s="226"/>
-      <c r="G146" s="226"/>
-      <c r="H146" s="226"/>
-      <c r="I146" s="226"/>
-      <c r="J146" s="226"/>
-      <c r="K146" s="226"/>
-      <c r="L146" s="227"/>
+      <c r="B146" s="232"/>
+      <c r="C146" s="232"/>
+      <c r="D146" s="232"/>
+      <c r="E146" s="232"/>
+      <c r="F146" s="232"/>
+      <c r="G146" s="232"/>
+      <c r="H146" s="232"/>
+      <c r="I146" s="232"/>
+      <c r="J146" s="232"/>
+      <c r="K146" s="232"/>
+      <c r="L146" s="192"/>
       <c r="M146" s="1"/>
       <c r="N146" s="1"/>
       <c r="O146" s="1"/>
@@ -9148,7 +9148,7 @@
       </c>
       <c r="D147" s="94"/>
       <c r="E147" s="177"/>
-      <c r="F147" s="228" t="s">
+      <c r="F147" s="233" t="s">
         <v>87</v>
       </c>
       <c r="G147" s="177"/>
@@ -9161,10 +9161,10 @@
       <c r="J147" s="185" t="s">
         <v>84</v>
       </c>
-      <c r="K147" s="222" t="s">
+      <c r="K147" s="228" t="s">
         <v>85</v>
       </c>
-      <c r="L147" s="223">
+      <c r="L147" s="229">
         <f>SUM(L149:L181)</f>
         <v>0</v>
       </c>
@@ -9189,13 +9189,13 @@
       <c r="C148" s="174"/>
       <c r="D148" s="112"/>
       <c r="E148" s="172"/>
-      <c r="F148" s="229"/>
+      <c r="F148" s="234"/>
       <c r="G148" s="172"/>
       <c r="H148" s="186"/>
       <c r="I148" s="186"/>
       <c r="J148" s="186"/>
       <c r="K148" s="188"/>
-      <c r="L148" s="224"/>
+      <c r="L148" s="230"/>
       <c r="M148" s="1"/>
       <c r="N148" s="1"/>
       <c r="O148" s="1"/>
@@ -9212,13 +9212,13 @@
       <c r="Z148" s="1"/>
     </row>
     <row r="149" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A149" s="210"/>
+      <c r="A149" s="216"/>
       <c r="B149" s="177"/>
-      <c r="C149" s="218"/>
+      <c r="C149" s="224"/>
       <c r="D149" s="114"/>
-      <c r="E149" s="212"/>
-      <c r="F149" s="218"/>
-      <c r="G149" s="212"/>
+      <c r="E149" s="218"/>
+      <c r="F149" s="224"/>
+      <c r="G149" s="218"/>
       <c r="H149" s="35"/>
       <c r="I149" s="36"/>
       <c r="J149" s="37"/>
@@ -9243,12 +9243,12 @@
       <c r="Z149" s="1"/>
     </row>
     <row r="150" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A150" s="210"/>
+      <c r="A150" s="216"/>
       <c r="B150" s="177"/>
-      <c r="C150" s="216"/>
+      <c r="C150" s="222"/>
       <c r="D150" s="87"/>
       <c r="E150" s="91"/>
-      <c r="F150" s="216"/>
+      <c r="F150" s="222"/>
       <c r="G150" s="91"/>
       <c r="H150" s="28"/>
       <c r="I150" s="26"/>
@@ -9274,12 +9274,12 @@
       <c r="Z150" s="1"/>
     </row>
     <row r="151" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A151" s="210"/>
+      <c r="A151" s="216"/>
       <c r="B151" s="177"/>
-      <c r="C151" s="216"/>
+      <c r="C151" s="222"/>
       <c r="D151" s="87"/>
       <c r="E151" s="91"/>
-      <c r="F151" s="216"/>
+      <c r="F151" s="222"/>
       <c r="G151" s="91"/>
       <c r="H151" s="28"/>
       <c r="I151" s="26"/>
@@ -9305,12 +9305,12 @@
       <c r="Z151" s="1"/>
     </row>
     <row r="152" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A152" s="210"/>
+      <c r="A152" s="216"/>
       <c r="B152" s="177"/>
-      <c r="C152" s="216"/>
+      <c r="C152" s="222"/>
       <c r="D152" s="87"/>
       <c r="E152" s="91"/>
-      <c r="F152" s="216"/>
+      <c r="F152" s="222"/>
       <c r="G152" s="91"/>
       <c r="H152" s="28"/>
       <c r="I152" s="26"/>
@@ -9336,12 +9336,12 @@
       <c r="Z152" s="1"/>
     </row>
     <row r="153" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A153" s="210"/>
+      <c r="A153" s="216"/>
       <c r="B153" s="177"/>
-      <c r="C153" s="216"/>
+      <c r="C153" s="222"/>
       <c r="D153" s="87"/>
       <c r="E153" s="91"/>
-      <c r="F153" s="216"/>
+      <c r="F153" s="222"/>
       <c r="G153" s="91"/>
       <c r="H153" s="28"/>
       <c r="I153" s="26"/>
@@ -9367,12 +9367,12 @@
       <c r="Z153" s="1"/>
     </row>
     <row r="154" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A154" s="210"/>
+      <c r="A154" s="216"/>
       <c r="B154" s="177"/>
-      <c r="C154" s="216"/>
+      <c r="C154" s="222"/>
       <c r="D154" s="87"/>
       <c r="E154" s="91"/>
-      <c r="F154" s="216"/>
+      <c r="F154" s="222"/>
       <c r="G154" s="91"/>
       <c r="H154" s="28"/>
       <c r="I154" s="26"/>
@@ -9398,12 +9398,12 @@
       <c r="Z154" s="1"/>
     </row>
     <row r="155" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A155" s="210"/>
+      <c r="A155" s="216"/>
       <c r="B155" s="177"/>
-      <c r="C155" s="216"/>
+      <c r="C155" s="222"/>
       <c r="D155" s="87"/>
       <c r="E155" s="91"/>
-      <c r="F155" s="216"/>
+      <c r="F155" s="222"/>
       <c r="G155" s="91"/>
       <c r="H155" s="28"/>
       <c r="I155" s="26"/>
@@ -9429,12 +9429,12 @@
       <c r="Z155" s="1"/>
     </row>
     <row r="156" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A156" s="210"/>
+      <c r="A156" s="216"/>
       <c r="B156" s="177"/>
-      <c r="C156" s="216"/>
+      <c r="C156" s="222"/>
       <c r="D156" s="87"/>
       <c r="E156" s="91"/>
-      <c r="F156" s="216"/>
+      <c r="F156" s="222"/>
       <c r="G156" s="91"/>
       <c r="H156" s="28"/>
       <c r="I156" s="26"/>
@@ -9460,12 +9460,12 @@
       <c r="Z156" s="1"/>
     </row>
     <row r="157" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A157" s="210"/>
+      <c r="A157" s="216"/>
       <c r="B157" s="177"/>
-      <c r="C157" s="216"/>
+      <c r="C157" s="222"/>
       <c r="D157" s="87"/>
       <c r="E157" s="91"/>
-      <c r="F157" s="216"/>
+      <c r="F157" s="222"/>
       <c r="G157" s="91"/>
       <c r="H157" s="28"/>
       <c r="I157" s="26"/>
@@ -9491,12 +9491,12 @@
       <c r="Z157" s="1"/>
     </row>
     <row r="158" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A158" s="210"/>
+      <c r="A158" s="216"/>
       <c r="B158" s="177"/>
-      <c r="C158" s="216"/>
+      <c r="C158" s="222"/>
       <c r="D158" s="87"/>
       <c r="E158" s="91"/>
-      <c r="F158" s="216"/>
+      <c r="F158" s="222"/>
       <c r="G158" s="91"/>
       <c r="H158" s="28"/>
       <c r="I158" s="26"/>
@@ -9522,12 +9522,12 @@
       <c r="Z158" s="1"/>
     </row>
     <row r="159" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A159" s="210"/>
+      <c r="A159" s="216"/>
       <c r="B159" s="177"/>
-      <c r="C159" s="216"/>
+      <c r="C159" s="222"/>
       <c r="D159" s="87"/>
       <c r="E159" s="91"/>
-      <c r="F159" s="216"/>
+      <c r="F159" s="222"/>
       <c r="G159" s="91"/>
       <c r="H159" s="28"/>
       <c r="I159" s="26"/>
@@ -9553,12 +9553,12 @@
       <c r="Z159" s="1"/>
     </row>
     <row r="160" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A160" s="210"/>
+      <c r="A160" s="216"/>
       <c r="B160" s="177"/>
-      <c r="C160" s="216"/>
+      <c r="C160" s="222"/>
       <c r="D160" s="87"/>
       <c r="E160" s="91"/>
-      <c r="F160" s="216"/>
+      <c r="F160" s="222"/>
       <c r="G160" s="91"/>
       <c r="H160" s="28"/>
       <c r="I160" s="26"/>
@@ -9584,12 +9584,12 @@
       <c r="Z160" s="1"/>
     </row>
     <row r="161" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A161" s="210"/>
+      <c r="A161" s="216"/>
       <c r="B161" s="177"/>
-      <c r="C161" s="216"/>
+      <c r="C161" s="222"/>
       <c r="D161" s="87"/>
       <c r="E161" s="91"/>
-      <c r="F161" s="216"/>
+      <c r="F161" s="222"/>
       <c r="G161" s="91"/>
       <c r="H161" s="28"/>
       <c r="I161" s="26"/>
@@ -9615,12 +9615,12 @@
       <c r="Z161" s="1"/>
     </row>
     <row r="162" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A162" s="210"/>
+      <c r="A162" s="216"/>
       <c r="B162" s="177"/>
-      <c r="C162" s="216"/>
+      <c r="C162" s="222"/>
       <c r="D162" s="87"/>
       <c r="E162" s="91"/>
-      <c r="F162" s="216"/>
+      <c r="F162" s="222"/>
       <c r="G162" s="91"/>
       <c r="H162" s="28"/>
       <c r="I162" s="26"/>
@@ -9646,12 +9646,12 @@
       <c r="Z162" s="1"/>
     </row>
     <row r="163" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A163" s="210"/>
+      <c r="A163" s="216"/>
       <c r="B163" s="177"/>
-      <c r="C163" s="216"/>
+      <c r="C163" s="222"/>
       <c r="D163" s="87"/>
       <c r="E163" s="91"/>
-      <c r="F163" s="216"/>
+      <c r="F163" s="222"/>
       <c r="G163" s="91"/>
       <c r="H163" s="28"/>
       <c r="I163" s="26"/>
@@ -9677,12 +9677,12 @@
       <c r="Z163" s="1"/>
     </row>
     <row r="164" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A164" s="210"/>
+      <c r="A164" s="216"/>
       <c r="B164" s="177"/>
-      <c r="C164" s="216"/>
+      <c r="C164" s="222"/>
       <c r="D164" s="87"/>
       <c r="E164" s="91"/>
-      <c r="F164" s="216"/>
+      <c r="F164" s="222"/>
       <c r="G164" s="91"/>
       <c r="H164" s="28"/>
       <c r="I164" s="26"/>
@@ -9708,12 +9708,12 @@
       <c r="Z164" s="1"/>
     </row>
     <row r="165" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A165" s="210"/>
+      <c r="A165" s="216"/>
       <c r="B165" s="177"/>
-      <c r="C165" s="216"/>
+      <c r="C165" s="222"/>
       <c r="D165" s="87"/>
       <c r="E165" s="91"/>
-      <c r="F165" s="216"/>
+      <c r="F165" s="222"/>
       <c r="G165" s="91"/>
       <c r="H165" s="28"/>
       <c r="I165" s="26"/>
@@ -9739,12 +9739,12 @@
       <c r="Z165" s="1"/>
     </row>
     <row r="166" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A166" s="210"/>
+      <c r="A166" s="216"/>
       <c r="B166" s="177"/>
-      <c r="C166" s="216"/>
+      <c r="C166" s="222"/>
       <c r="D166" s="87"/>
       <c r="E166" s="91"/>
-      <c r="F166" s="216"/>
+      <c r="F166" s="222"/>
       <c r="G166" s="91"/>
       <c r="H166" s="28"/>
       <c r="I166" s="26"/>
@@ -9770,12 +9770,12 @@
       <c r="Z166" s="1"/>
     </row>
     <row r="167" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A167" s="210"/>
+      <c r="A167" s="216"/>
       <c r="B167" s="177"/>
-      <c r="C167" s="216"/>
+      <c r="C167" s="222"/>
       <c r="D167" s="87"/>
       <c r="E167" s="91"/>
-      <c r="F167" s="216"/>
+      <c r="F167" s="222"/>
       <c r="G167" s="91"/>
       <c r="H167" s="28"/>
       <c r="I167" s="26"/>
@@ -9801,12 +9801,12 @@
       <c r="Z167" s="1"/>
     </row>
     <row r="168" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A168" s="210"/>
+      <c r="A168" s="216"/>
       <c r="B168" s="177"/>
-      <c r="C168" s="216"/>
+      <c r="C168" s="222"/>
       <c r="D168" s="87"/>
       <c r="E168" s="91"/>
-      <c r="F168" s="216"/>
+      <c r="F168" s="222"/>
       <c r="G168" s="91"/>
       <c r="H168" s="28"/>
       <c r="I168" s="26"/>
@@ -9832,12 +9832,12 @@
       <c r="Z168" s="1"/>
     </row>
     <row r="169" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A169" s="210"/>
+      <c r="A169" s="216"/>
       <c r="B169" s="177"/>
-      <c r="C169" s="216"/>
+      <c r="C169" s="222"/>
       <c r="D169" s="87"/>
       <c r="E169" s="91"/>
-      <c r="F169" s="216"/>
+      <c r="F169" s="222"/>
       <c r="G169" s="91"/>
       <c r="H169" s="28"/>
       <c r="I169" s="26"/>
@@ -9863,12 +9863,12 @@
       <c r="Z169" s="1"/>
     </row>
     <row r="170" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A170" s="210"/>
+      <c r="A170" s="216"/>
       <c r="B170" s="177"/>
-      <c r="C170" s="216"/>
+      <c r="C170" s="222"/>
       <c r="D170" s="87"/>
       <c r="E170" s="91"/>
-      <c r="F170" s="216"/>
+      <c r="F170" s="222"/>
       <c r="G170" s="91"/>
       <c r="H170" s="28"/>
       <c r="I170" s="26"/>
@@ -9894,12 +9894,12 @@
       <c r="Z170" s="1"/>
     </row>
     <row r="171" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A171" s="210"/>
+      <c r="A171" s="216"/>
       <c r="B171" s="177"/>
-      <c r="C171" s="216"/>
+      <c r="C171" s="222"/>
       <c r="D171" s="87"/>
       <c r="E171" s="91"/>
-      <c r="F171" s="216"/>
+      <c r="F171" s="222"/>
       <c r="G171" s="91"/>
       <c r="H171" s="28"/>
       <c r="I171" s="26"/>
@@ -9925,12 +9925,12 @@
       <c r="Z171" s="1"/>
     </row>
     <row r="172" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A172" s="210"/>
+      <c r="A172" s="216"/>
       <c r="B172" s="177"/>
-      <c r="C172" s="216"/>
+      <c r="C172" s="222"/>
       <c r="D172" s="87"/>
       <c r="E172" s="91"/>
-      <c r="F172" s="216"/>
+      <c r="F172" s="222"/>
       <c r="G172" s="91"/>
       <c r="H172" s="28"/>
       <c r="I172" s="26"/>
@@ -9956,12 +9956,12 @@
       <c r="Z172" s="1"/>
     </row>
     <row r="173" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A173" s="210"/>
+      <c r="A173" s="216"/>
       <c r="B173" s="177"/>
-      <c r="C173" s="216"/>
+      <c r="C173" s="222"/>
       <c r="D173" s="87"/>
       <c r="E173" s="91"/>
-      <c r="F173" s="216"/>
+      <c r="F173" s="222"/>
       <c r="G173" s="91"/>
       <c r="H173" s="28"/>
       <c r="I173" s="26"/>
@@ -9987,12 +9987,12 @@
       <c r="Z173" s="1"/>
     </row>
     <row r="174" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A174" s="210"/>
+      <c r="A174" s="216"/>
       <c r="B174" s="177"/>
-      <c r="C174" s="216"/>
+      <c r="C174" s="222"/>
       <c r="D174" s="87"/>
       <c r="E174" s="91"/>
-      <c r="F174" s="216"/>
+      <c r="F174" s="222"/>
       <c r="G174" s="91"/>
       <c r="H174" s="28"/>
       <c r="I174" s="26"/>
@@ -10018,12 +10018,12 @@
       <c r="Z174" s="1"/>
     </row>
     <row r="175" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A175" s="210"/>
+      <c r="A175" s="216"/>
       <c r="B175" s="177"/>
-      <c r="C175" s="216"/>
+      <c r="C175" s="222"/>
       <c r="D175" s="87"/>
       <c r="E175" s="91"/>
-      <c r="F175" s="216"/>
+      <c r="F175" s="222"/>
       <c r="G175" s="91"/>
       <c r="H175" s="28"/>
       <c r="I175" s="26"/>
@@ -10049,12 +10049,12 @@
       <c r="Z175" s="1"/>
     </row>
     <row r="176" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A176" s="210"/>
+      <c r="A176" s="216"/>
       <c r="B176" s="177"/>
-      <c r="C176" s="216"/>
+      <c r="C176" s="222"/>
       <c r="D176" s="87"/>
       <c r="E176" s="91"/>
-      <c r="F176" s="216"/>
+      <c r="F176" s="222"/>
       <c r="G176" s="91"/>
       <c r="H176" s="28"/>
       <c r="I176" s="26"/>
@@ -10080,12 +10080,12 @@
       <c r="Z176" s="1"/>
     </row>
     <row r="177" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A177" s="210"/>
+      <c r="A177" s="216"/>
       <c r="B177" s="177"/>
-      <c r="C177" s="216"/>
+      <c r="C177" s="222"/>
       <c r="D177" s="87"/>
       <c r="E177" s="91"/>
-      <c r="F177" s="216"/>
+      <c r="F177" s="222"/>
       <c r="G177" s="91"/>
       <c r="H177" s="28"/>
       <c r="I177" s="26"/>
@@ -10111,12 +10111,12 @@
       <c r="Z177" s="1"/>
     </row>
     <row r="178" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A178" s="210"/>
+      <c r="A178" s="216"/>
       <c r="B178" s="177"/>
-      <c r="C178" s="216"/>
+      <c r="C178" s="222"/>
       <c r="D178" s="87"/>
       <c r="E178" s="91"/>
-      <c r="F178" s="216"/>
+      <c r="F178" s="222"/>
       <c r="G178" s="91"/>
       <c r="H178" s="28"/>
       <c r="I178" s="26"/>
@@ -10142,12 +10142,12 @@
       <c r="Z178" s="1"/>
     </row>
     <row r="179" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A179" s="210"/>
+      <c r="A179" s="216"/>
       <c r="B179" s="177"/>
-      <c r="C179" s="216"/>
+      <c r="C179" s="222"/>
       <c r="D179" s="87"/>
       <c r="E179" s="91"/>
-      <c r="F179" s="216"/>
+      <c r="F179" s="222"/>
       <c r="G179" s="91"/>
       <c r="H179" s="28"/>
       <c r="I179" s="26"/>
@@ -10173,12 +10173,12 @@
       <c r="Z179" s="1"/>
     </row>
     <row r="180" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A180" s="210"/>
+      <c r="A180" s="216"/>
       <c r="B180" s="177"/>
-      <c r="C180" s="216"/>
+      <c r="C180" s="222"/>
       <c r="D180" s="87"/>
       <c r="E180" s="91"/>
-      <c r="F180" s="216"/>
+      <c r="F180" s="222"/>
       <c r="G180" s="91"/>
       <c r="H180" s="28"/>
       <c r="I180" s="26"/>
@@ -10204,12 +10204,12 @@
       <c r="Z180" s="1"/>
     </row>
     <row r="181" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A181" s="219"/>
+      <c r="A181" s="225"/>
       <c r="B181" s="91"/>
-      <c r="C181" s="220"/>
+      <c r="C181" s="226"/>
       <c r="D181" s="162"/>
       <c r="E181" s="158"/>
-      <c r="F181" s="220"/>
+      <c r="F181" s="226"/>
       <c r="G181" s="158"/>
       <c r="H181" s="30"/>
       <c r="I181" s="31"/>
@@ -10263,7 +10263,7 @@
       <c r="Z182" s="1"/>
     </row>
     <row r="183" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A183" s="230" t="s">
+      <c r="A183" s="235" t="s">
         <v>89</v>
       </c>
       <c r="B183" s="94"/>
@@ -10275,7 +10275,7 @@
       <c r="H183" s="94"/>
       <c r="I183" s="94"/>
       <c r="J183" s="95"/>
-      <c r="K183" s="231"/>
+      <c r="K183" s="236"/>
       <c r="L183" s="95"/>
       <c r="M183" s="1"/>
       <c r="N183" s="1"/>
@@ -10349,7 +10349,7 @@
       <c r="Z185" s="1"/>
     </row>
     <row r="186" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A186" s="232" t="s">
+      <c r="A186" s="237" t="s">
         <v>90</v>
       </c>
       <c r="B186" s="94"/>
@@ -10361,7 +10361,7 @@
       <c r="H186" s="94"/>
       <c r="I186" s="94"/>
       <c r="J186" s="177"/>
-      <c r="K186" s="233"/>
+      <c r="K186" s="238"/>
       <c r="L186" s="95"/>
       <c r="M186" s="1"/>
       <c r="N186" s="1"/>
@@ -10435,7 +10435,7 @@
       <c r="Z188" s="1"/>
     </row>
     <row r="189" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A189" s="232" t="s">
+      <c r="A189" s="237" t="s">
         <v>91</v>
       </c>
       <c r="B189" s="94"/>
@@ -10447,7 +10447,7 @@
       <c r="H189" s="94"/>
       <c r="I189" s="94"/>
       <c r="J189" s="177"/>
-      <c r="K189" s="233"/>
+      <c r="K189" s="238"/>
       <c r="L189" s="95"/>
       <c r="M189" s="1"/>
       <c r="N189" s="1"/>
@@ -10521,19 +10521,19 @@
       <c r="Z191" s="1"/>
     </row>
     <row r="192" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A192" s="234" t="s">
+      <c r="A192" s="239" t="s">
         <v>92</v>
       </c>
-      <c r="B192" s="226"/>
-      <c r="C192" s="226"/>
-      <c r="D192" s="226"/>
-      <c r="E192" s="226"/>
-      <c r="F192" s="226"/>
-      <c r="G192" s="226"/>
-      <c r="H192" s="226"/>
-      <c r="I192" s="226"/>
-      <c r="J192" s="235"/>
-      <c r="K192" s="233"/>
+      <c r="B192" s="232"/>
+      <c r="C192" s="232"/>
+      <c r="D192" s="232"/>
+      <c r="E192" s="232"/>
+      <c r="F192" s="232"/>
+      <c r="G192" s="232"/>
+      <c r="H192" s="232"/>
+      <c r="I192" s="232"/>
+      <c r="J192" s="240"/>
+      <c r="K192" s="238"/>
       <c r="L192" s="95"/>
       <c r="M192" s="1"/>
       <c r="N192" s="1"/>
@@ -10551,18 +10551,18 @@
       <c r="Z192" s="1"/>
     </row>
     <row r="193" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A193" s="236" t="s">
+      <c r="A193" s="241" t="s">
         <v>93</v>
       </c>
-      <c r="B193" s="237"/>
-      <c r="C193" s="237"/>
-      <c r="D193" s="237"/>
-      <c r="E193" s="237"/>
-      <c r="F193" s="237"/>
-      <c r="G193" s="237"/>
-      <c r="H193" s="237"/>
-      <c r="I193" s="237"/>
-      <c r="J193" s="238"/>
+      <c r="B193" s="242"/>
+      <c r="C193" s="242"/>
+      <c r="D193" s="242"/>
+      <c r="E193" s="242"/>
+      <c r="F193" s="242"/>
+      <c r="G193" s="242"/>
+      <c r="H193" s="242"/>
+      <c r="I193" s="242"/>
+      <c r="J193" s="243"/>
       <c r="K193" s="174"/>
       <c r="L193" s="166"/>
       <c r="M193" s="1"/>
@@ -10609,7 +10609,7 @@
       <c r="Z194" s="1"/>
     </row>
     <row r="195" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A195" s="232" t="s">
+      <c r="A195" s="237" t="s">
         <v>94</v>
       </c>
       <c r="B195" s="94"/>
@@ -10621,7 +10621,7 @@
       <c r="H195" s="94"/>
       <c r="I195" s="94"/>
       <c r="J195" s="177"/>
-      <c r="K195" s="239"/>
+      <c r="K195" s="244"/>
       <c r="L195" s="95"/>
       <c r="M195" s="1"/>
       <c r="N195" s="1"/>
@@ -10695,7 +10695,7 @@
       <c r="Z197" s="1"/>
     </row>
     <row r="198" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A198" s="232" t="s">
+      <c r="A198" s="237" t="s">
         <v>95</v>
       </c>
       <c r="B198" s="94"/>
@@ -10707,7 +10707,7 @@
       <c r="H198" s="94"/>
       <c r="I198" s="94"/>
       <c r="J198" s="177"/>
-      <c r="K198" s="233"/>
+      <c r="K198" s="238"/>
       <c r="L198" s="95"/>
       <c r="M198" s="1"/>
       <c r="N198" s="1"/>
@@ -10781,7 +10781,7 @@
       <c r="Z200" s="1"/>
     </row>
     <row r="201" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A201" s="232" t="s">
+      <c r="A201" s="237" t="s">
         <v>96</v>
       </c>
       <c r="B201" s="94"/>
@@ -10793,7 +10793,7 @@
       <c r="H201" s="94"/>
       <c r="I201" s="94"/>
       <c r="J201" s="177"/>
-      <c r="K201" s="233">
+      <c r="K201" s="238">
         <f>K332</f>
         <v>0</v>
       </c>
@@ -10870,7 +10870,7 @@
       <c r="Z203" s="1"/>
     </row>
     <row r="204" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A204" s="232" t="s">
+      <c r="A204" s="237" t="s">
         <v>97</v>
       </c>
       <c r="B204" s="94"/>
@@ -10882,7 +10882,7 @@
       <c r="H204" s="94"/>
       <c r="I204" s="94"/>
       <c r="J204" s="177"/>
-      <c r="K204" s="239"/>
+      <c r="K204" s="244"/>
       <c r="L204" s="95"/>
       <c r="M204" s="1"/>
       <c r="N204" s="1"/>
@@ -10968,7 +10968,7 @@
       <c r="H207" s="94"/>
       <c r="I207" s="94"/>
       <c r="J207" s="177"/>
-      <c r="K207" s="240">
+      <c r="K207" s="245">
         <f>(+K183+L112+K186+K189+K195+L147+K198+K192)*K209</f>
         <v>0</v>
       </c>
@@ -11017,7 +11017,7 @@
       <c r="Z208" s="1"/>
     </row>
     <row r="209" spans="1:26" ht="18" customHeight="1">
-      <c r="A209" s="241" t="s">
+      <c r="A209" s="246" t="s">
         <v>99</v>
       </c>
       <c r="B209" s="103"/>
@@ -11029,7 +11029,7 @@
       <c r="H209" s="103"/>
       <c r="I209" s="103"/>
       <c r="J209" s="100"/>
-      <c r="K209" s="242"/>
+      <c r="K209" s="247"/>
       <c r="L209" s="104"/>
       <c r="M209" s="1"/>
       <c r="N209" s="1"/>
@@ -11075,7 +11075,7 @@
       <c r="Z210" s="1"/>
     </row>
     <row r="211" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A211" s="243" t="s">
+      <c r="A211" s="248" t="s">
         <v>100</v>
       </c>
       <c r="B211" s="103"/>
@@ -11118,8 +11118,8 @@
       <c r="H212" s="111"/>
       <c r="I212" s="111"/>
       <c r="J212" s="135"/>
-      <c r="K212" s="198"/>
-      <c r="L212" s="244"/>
+      <c r="K212" s="204"/>
+      <c r="L212" s="249"/>
       <c r="M212" s="1"/>
       <c r="N212" s="1"/>
       <c r="O212" s="1"/>
@@ -11164,7 +11164,7 @@
       <c r="Z213" s="1"/>
     </row>
     <row r="214" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A214" s="241" t="s">
+      <c r="A214" s="246" t="s">
         <v>101</v>
       </c>
       <c r="B214" s="103"/>
@@ -11176,7 +11176,7 @@
       <c r="H214" s="103"/>
       <c r="I214" s="103"/>
       <c r="J214" s="100"/>
-      <c r="K214" s="245"/>
+      <c r="K214" s="250"/>
       <c r="L214" s="104"/>
       <c r="M214" s="1"/>
       <c r="N214" s="1"/>
@@ -11222,7 +11222,7 @@
       <c r="Z215" s="1"/>
     </row>
     <row r="216" spans="1:26" ht="18" customHeight="1">
-      <c r="A216" s="247" t="s">
+      <c r="A216" s="252" t="s">
         <v>102</v>
       </c>
       <c r="B216" s="103"/>
@@ -11369,14 +11369,14 @@
       <c r="Z220" s="1"/>
     </row>
     <row r="221" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A221" s="247" t="s">
+      <c r="A221" s="252" t="s">
         <v>104</v>
       </c>
       <c r="B221" s="100"/>
-      <c r="C221" s="248" t="s">
+      <c r="C221" s="253" t="s">
         <v>105</v>
       </c>
-      <c r="D221" s="246" t="s">
+      <c r="D221" s="251" t="s">
         <v>106</v>
       </c>
       <c r="E221" s="103"/>
@@ -11385,7 +11385,7 @@
       <c r="H221" s="103"/>
       <c r="I221" s="103"/>
       <c r="J221" s="100"/>
-      <c r="K221" s="250" t="s">
+      <c r="K221" s="255" t="s">
         <v>107</v>
       </c>
       <c r="L221" s="88"/>
@@ -11407,15 +11407,15 @@
     <row r="222" spans="1:26" ht="66" customHeight="1">
       <c r="A222" s="155"/>
       <c r="B222" s="135"/>
-      <c r="C222" s="249"/>
-      <c r="D222" s="198"/>
+      <c r="C222" s="254"/>
+      <c r="D222" s="204"/>
       <c r="E222" s="111"/>
       <c r="F222" s="111"/>
       <c r="G222" s="111"/>
       <c r="H222" s="111"/>
       <c r="I222" s="111"/>
       <c r="J222" s="135"/>
-      <c r="K222" s="251" t="s">
+      <c r="K222" s="256" t="s">
         <v>108</v>
       </c>
       <c r="L222" s="88"/>
@@ -11467,10 +11467,10 @@
       <c r="Z223" s="1"/>
     </row>
     <row r="224" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A224" s="252"/>
+      <c r="A224" s="257"/>
       <c r="B224" s="91"/>
       <c r="C224" s="50"/>
-      <c r="D224" s="216" t="s">
+      <c r="D224" s="222" t="s">
         <v>111</v>
       </c>
       <c r="E224" s="87"/>
@@ -11497,10 +11497,10 @@
       <c r="Z224" s="1"/>
     </row>
     <row r="225" spans="1:26" ht="19.5" customHeight="1">
-      <c r="A225" s="252"/>
+      <c r="A225" s="257"/>
       <c r="B225" s="91"/>
       <c r="C225" s="50"/>
-      <c r="D225" s="216" t="s">
+      <c r="D225" s="222" t="s">
         <v>111</v>
       </c>
       <c r="E225" s="87"/>
@@ -11527,10 +11527,10 @@
       <c r="Z225" s="1"/>
     </row>
     <row r="226" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A226" s="252"/>
+      <c r="A226" s="257"/>
       <c r="B226" s="91"/>
       <c r="C226" s="50"/>
-      <c r="D226" s="216" t="s">
+      <c r="D226" s="222" t="s">
         <v>111</v>
       </c>
       <c r="E226" s="87"/>
@@ -11557,10 +11557,10 @@
       <c r="Z226" s="1"/>
     </row>
     <row r="227" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A227" s="252"/>
+      <c r="A227" s="257"/>
       <c r="B227" s="91"/>
       <c r="C227" s="50"/>
-      <c r="D227" s="216" t="s">
+      <c r="D227" s="222" t="s">
         <v>111</v>
       </c>
       <c r="E227" s="87"/>
@@ -11587,10 +11587,10 @@
       <c r="Z227" s="1"/>
     </row>
     <row r="228" spans="1:26" ht="24" customHeight="1">
-      <c r="A228" s="252"/>
+      <c r="A228" s="257"/>
       <c r="B228" s="91"/>
       <c r="C228" s="50"/>
-      <c r="D228" s="264" t="s">
+      <c r="D228" s="269" t="s">
         <v>111</v>
       </c>
       <c r="E228" s="87"/>
@@ -11620,7 +11620,7 @@
       <c r="A229" s="53"/>
       <c r="B229" s="54"/>
       <c r="C229" s="55"/>
-      <c r="D229" s="264" t="s">
+      <c r="D229" s="269" t="s">
         <v>111</v>
       </c>
       <c r="E229" s="87"/>
@@ -11650,7 +11650,7 @@
       <c r="A230" s="53"/>
       <c r="B230" s="54"/>
       <c r="C230" s="55"/>
-      <c r="D230" s="264" t="s">
+      <c r="D230" s="269" t="s">
         <v>111</v>
       </c>
       <c r="E230" s="87"/>
@@ -11680,7 +11680,7 @@
       <c r="A231" s="53"/>
       <c r="B231" s="54"/>
       <c r="C231" s="55"/>
-      <c r="D231" s="264" t="s">
+      <c r="D231" s="269" t="s">
         <v>111</v>
       </c>
       <c r="E231" s="87"/>
@@ -11710,7 +11710,7 @@
       <c r="A232" s="53"/>
       <c r="B232" s="54"/>
       <c r="C232" s="55"/>
-      <c r="D232" s="264" t="s">
+      <c r="D232" s="269" t="s">
         <v>111</v>
       </c>
       <c r="E232" s="87"/>
@@ -11740,7 +11740,7 @@
       <c r="A233" s="53"/>
       <c r="B233" s="54"/>
       <c r="C233" s="55"/>
-      <c r="D233" s="264" t="s">
+      <c r="D233" s="269" t="s">
         <v>111</v>
       </c>
       <c r="E233" s="87"/>
@@ -11770,7 +11770,7 @@
       <c r="A234" s="53"/>
       <c r="B234" s="54"/>
       <c r="C234" s="55"/>
-      <c r="D234" s="264" t="s">
+      <c r="D234" s="269" t="s">
         <v>111</v>
       </c>
       <c r="E234" s="87"/>
@@ -11800,7 +11800,7 @@
       <c r="A235" s="53"/>
       <c r="B235" s="54"/>
       <c r="C235" s="55"/>
-      <c r="D235" s="264" t="s">
+      <c r="D235" s="269" t="s">
         <v>111</v>
       </c>
       <c r="E235" s="87"/>
@@ -11830,7 +11830,7 @@
       <c r="A236" s="53"/>
       <c r="B236" s="54"/>
       <c r="C236" s="55"/>
-      <c r="D236" s="264" t="s">
+      <c r="D236" s="269" t="s">
         <v>111</v>
       </c>
       <c r="E236" s="87"/>
@@ -11857,7 +11857,7 @@
       <c r="Z236" s="1"/>
     </row>
     <row r="237" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A237" s="265"/>
+      <c r="A237" s="270"/>
       <c r="B237" s="162"/>
       <c r="C237" s="162"/>
       <c r="D237" s="162"/>
@@ -11867,7 +11867,7 @@
       <c r="H237" s="162"/>
       <c r="I237" s="162"/>
       <c r="J237" s="158"/>
-      <c r="K237" s="266"/>
+      <c r="K237" s="271"/>
       <c r="L237" s="163"/>
       <c r="M237" s="1"/>
       <c r="N237" s="1"/>
@@ -11971,7 +11971,7 @@
       <c r="Z240" s="1"/>
     </row>
     <row r="241" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A241" s="267" t="s">
+      <c r="A241" s="272" t="s">
         <v>113</v>
       </c>
       <c r="B241" s="87"/>
@@ -12505,7 +12505,7 @@
       <c r="Z257" s="1"/>
     </row>
     <row r="258" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A258" s="271" t="s">
+      <c r="A258" s="276" t="s">
         <v>116</v>
       </c>
       <c r="B258" s="117"/>
@@ -12535,7 +12535,7 @@
       <c r="Z258" s="1"/>
     </row>
     <row r="259" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A259" s="271" t="s">
+      <c r="A259" s="276" t="s">
         <v>117</v>
       </c>
       <c r="B259" s="117"/>
@@ -12652,14 +12652,14 @@
     </row>
     <row r="263" spans="1:26" ht="18.75" customHeight="1">
       <c r="A263" s="61"/>
-      <c r="B263" s="272" t="s">
+      <c r="B263" s="277" t="s">
         <v>119</v>
       </c>
       <c r="C263" s="117"/>
       <c r="D263" s="117"/>
       <c r="E263" s="118"/>
       <c r="F263" s="62"/>
-      <c r="G263" s="273" t="s">
+      <c r="G263" s="278" t="s">
         <v>120</v>
       </c>
       <c r="H263" s="114"/>
@@ -12700,11 +12700,11 @@
       <c r="G264" s="68" t="s">
         <v>122</v>
       </c>
-      <c r="H264" s="274" t="s">
+      <c r="H264" s="279" t="s">
         <v>123</v>
       </c>
       <c r="I264" s="158"/>
-      <c r="J264" s="274" t="s">
+      <c r="J264" s="279" t="s">
         <v>68</v>
       </c>
       <c r="K264" s="163"/>
@@ -12735,7 +12735,7 @@
       </c>
       <c r="E265" s="71"/>
       <c r="F265" s="1"/>
-      <c r="G265" s="275"/>
+      <c r="G265" s="280"/>
       <c r="H265" s="94"/>
       <c r="I265" s="94"/>
       <c r="J265" s="94"/>
@@ -12799,14 +12799,14 @@
       </c>
       <c r="E267" s="71"/>
       <c r="F267" s="1"/>
-      <c r="G267" s="277" t="s">
+      <c r="G267" s="282" t="s">
         <v>124</v>
       </c>
-      <c r="H267" s="279" t="s">
+      <c r="H267" s="284" t="s">
         <v>125</v>
       </c>
       <c r="I267" s="91"/>
-      <c r="J267" s="280"/>
+      <c r="J267" s="285"/>
       <c r="K267" s="88"/>
       <c r="L267" s="69"/>
       <c r="M267" s="1"/>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E268" s="71"/>
       <c r="F268" s="1"/>
-      <c r="G268" s="278"/>
-      <c r="H268" s="281" t="s">
+      <c r="G268" s="283"/>
+      <c r="H268" s="286" t="s">
         <v>126</v>
       </c>
       <c r="I268" s="158"/>
-      <c r="J268" s="282"/>
+      <c r="J268" s="287"/>
       <c r="K268" s="163"/>
       <c r="L268" s="69"/>
       <c r="M268" s="1"/>
@@ -12869,7 +12869,7 @@
       </c>
       <c r="E269" s="71"/>
       <c r="F269" s="1"/>
-      <c r="G269" s="275"/>
+      <c r="G269" s="280"/>
       <c r="H269" s="94"/>
       <c r="I269" s="94"/>
       <c r="J269" s="94"/>
@@ -12933,14 +12933,14 @@
       </c>
       <c r="E271" s="71"/>
       <c r="F271" s="1"/>
-      <c r="G271" s="277" t="s">
+      <c r="G271" s="282" t="s">
         <v>127</v>
       </c>
-      <c r="H271" s="279" t="s">
+      <c r="H271" s="284" t="s">
         <v>125</v>
       </c>
       <c r="I271" s="91"/>
-      <c r="J271" s="280"/>
+      <c r="J271" s="285"/>
       <c r="K271" s="88"/>
       <c r="L271" s="69"/>
       <c r="M271" s="1"/>
@@ -12969,12 +12969,12 @@
       </c>
       <c r="E272" s="71"/>
       <c r="F272" s="1"/>
-      <c r="G272" s="278"/>
-      <c r="H272" s="281" t="s">
+      <c r="G272" s="283"/>
+      <c r="H272" s="286" t="s">
         <v>126</v>
       </c>
       <c r="I272" s="158"/>
-      <c r="J272" s="282"/>
+      <c r="J272" s="287"/>
       <c r="K272" s="163"/>
       <c r="L272" s="69"/>
       <c r="M272" s="1"/>
@@ -13003,7 +13003,7 @@
       </c>
       <c r="E273" s="71"/>
       <c r="F273" s="1"/>
-      <c r="G273" s="275"/>
+      <c r="G273" s="280"/>
       <c r="H273" s="94"/>
       <c r="I273" s="94"/>
       <c r="J273" s="94"/>
@@ -13067,14 +13067,14 @@
       </c>
       <c r="E275" s="71"/>
       <c r="F275" s="1"/>
-      <c r="G275" s="277" t="s">
+      <c r="G275" s="282" t="s">
         <v>128</v>
       </c>
-      <c r="H275" s="279" t="s">
+      <c r="H275" s="284" t="s">
         <v>125</v>
       </c>
       <c r="I275" s="91"/>
-      <c r="J275" s="280"/>
+      <c r="J275" s="285"/>
       <c r="K275" s="88"/>
       <c r="L275" s="69"/>
       <c r="M275" s="1"/>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E276" s="71"/>
       <c r="F276" s="1"/>
-      <c r="G276" s="278"/>
-      <c r="H276" s="281" t="s">
+      <c r="G276" s="283"/>
+      <c r="H276" s="286" t="s">
         <v>126</v>
       </c>
       <c r="I276" s="158"/>
-      <c r="J276" s="282"/>
+      <c r="J276" s="287"/>
       <c r="K276" s="163"/>
       <c r="L276" s="69"/>
       <c r="M276" s="1"/>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="E277" s="71"/>
       <c r="F277" s="1"/>
-      <c r="G277" s="275"/>
+      <c r="G277" s="280"/>
       <c r="H277" s="94"/>
       <c r="I277" s="94"/>
       <c r="J277" s="94"/>
@@ -13201,14 +13201,14 @@
       </c>
       <c r="E279" s="71"/>
       <c r="F279" s="1"/>
-      <c r="G279" s="277" t="s">
+      <c r="G279" s="282" t="s">
         <v>129</v>
       </c>
-      <c r="H279" s="279" t="s">
+      <c r="H279" s="284" t="s">
         <v>125</v>
       </c>
       <c r="I279" s="91"/>
-      <c r="J279" s="280"/>
+      <c r="J279" s="285"/>
       <c r="K279" s="88"/>
       <c r="L279" s="69"/>
       <c r="M279" s="1"/>
@@ -13237,12 +13237,12 @@
       </c>
       <c r="E280" s="71"/>
       <c r="F280" s="1"/>
-      <c r="G280" s="278"/>
-      <c r="H280" s="281" t="s">
+      <c r="G280" s="283"/>
+      <c r="H280" s="286" t="s">
         <v>126</v>
       </c>
       <c r="I280" s="158"/>
-      <c r="J280" s="282"/>
+      <c r="J280" s="287"/>
       <c r="K280" s="163"/>
       <c r="L280" s="69"/>
       <c r="M280" s="1"/>
@@ -13271,7 +13271,7 @@
       </c>
       <c r="E281" s="71"/>
       <c r="F281" s="1"/>
-      <c r="G281" s="286"/>
+      <c r="G281" s="291"/>
       <c r="H281" s="131"/>
       <c r="I281" s="131"/>
       <c r="J281" s="131"/>
@@ -13335,14 +13335,14 @@
       </c>
       <c r="E283" s="71"/>
       <c r="F283" s="1"/>
-      <c r="G283" s="285" t="s">
+      <c r="G283" s="290" t="s">
         <v>130</v>
       </c>
-      <c r="H283" s="287" t="s">
+      <c r="H283" s="292" t="s">
         <v>125</v>
       </c>
-      <c r="I283" s="288"/>
-      <c r="J283" s="289"/>
+      <c r="I283" s="293"/>
+      <c r="J283" s="294"/>
       <c r="K283" s="122"/>
       <c r="L283" s="69"/>
       <c r="M283" s="1"/>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E284" s="71"/>
       <c r="F284" s="1"/>
-      <c r="G284" s="278"/>
-      <c r="H284" s="281" t="s">
+      <c r="G284" s="283"/>
+      <c r="H284" s="286" t="s">
         <v>126</v>
       </c>
       <c r="I284" s="158"/>
-      <c r="J284" s="282"/>
+      <c r="J284" s="287"/>
       <c r="K284" s="163"/>
       <c r="L284" s="69"/>
       <c r="M284" s="1"/>
@@ -13405,16 +13405,16 @@
       </c>
       <c r="E285" s="71"/>
       <c r="F285" s="1"/>
-      <c r="G285" s="276" t="s">
+      <c r="G285" s="281" t="s">
         <v>55</v>
       </c>
-      <c r="H285" s="237"/>
-      <c r="I285" s="238"/>
-      <c r="J285" s="283">
+      <c r="H285" s="242"/>
+      <c r="I285" s="243"/>
+      <c r="J285" s="288">
         <f>SUM(J267,J268,J271,J272,J275,J276,J279,J280,J283,J284)</f>
         <v>0</v>
       </c>
-      <c r="K285" s="284"/>
+      <c r="K285" s="289"/>
       <c r="L285" s="69"/>
       <c r="M285" s="1"/>
       <c r="N285" s="1"/>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="E287" s="71"/>
       <c r="F287" s="1"/>
-      <c r="G287" s="268" t="s">
+      <c r="G287" s="273" t="s">
         <v>131</v>
       </c>
       <c r="H287" s="117"/>
@@ -13508,11 +13508,11 @@
       </c>
       <c r="E288" s="71"/>
       <c r="F288" s="1"/>
-      <c r="G288" s="269" t="s">
+      <c r="G288" s="274" t="s">
         <v>122</v>
       </c>
-      <c r="H288" s="212"/>
-      <c r="I288" s="270" t="s">
+      <c r="H288" s="218"/>
+      <c r="I288" s="275" t="s">
         <v>68</v>
       </c>
       <c r="J288" s="115"/>
@@ -13544,11 +13544,11 @@
       </c>
       <c r="E289" s="71"/>
       <c r="F289" s="1"/>
-      <c r="G289" s="256" t="s">
+      <c r="G289" s="261" t="s">
         <v>132</v>
       </c>
       <c r="H289" s="91"/>
-      <c r="I289" s="254"/>
+      <c r="I289" s="259"/>
       <c r="J289" s="88"/>
       <c r="K289" s="1"/>
       <c r="L289" s="73"/>
@@ -13578,11 +13578,11 @@
       </c>
       <c r="E290" s="71"/>
       <c r="F290" s="1"/>
-      <c r="G290" s="256" t="s">
+      <c r="G290" s="261" t="s">
         <v>133</v>
       </c>
       <c r="H290" s="91"/>
-      <c r="I290" s="254"/>
+      <c r="I290" s="259"/>
       <c r="J290" s="88"/>
       <c r="K290" s="1"/>
       <c r="L290" s="73"/>
@@ -13612,11 +13612,11 @@
       </c>
       <c r="E291" s="71"/>
       <c r="F291" s="1"/>
-      <c r="G291" s="256" t="s">
+      <c r="G291" s="261" t="s">
         <v>134</v>
       </c>
       <c r="H291" s="91"/>
-      <c r="I291" s="254"/>
+      <c r="I291" s="259"/>
       <c r="J291" s="88"/>
       <c r="K291" s="1"/>
       <c r="L291" s="73"/>
@@ -13646,11 +13646,11 @@
       </c>
       <c r="E292" s="71"/>
       <c r="F292" s="1"/>
-      <c r="G292" s="256" t="s">
+      <c r="G292" s="261" t="s">
         <v>135</v>
       </c>
       <c r="H292" s="91"/>
-      <c r="I292" s="254"/>
+      <c r="I292" s="259"/>
       <c r="J292" s="88"/>
       <c r="K292" s="1"/>
       <c r="L292" s="73"/>
@@ -13680,11 +13680,11 @@
       </c>
       <c r="E293" s="71"/>
       <c r="F293" s="1"/>
-      <c r="G293" s="256" t="s">
+      <c r="G293" s="261" t="s">
         <v>136</v>
       </c>
       <c r="H293" s="91"/>
-      <c r="I293" s="254"/>
+      <c r="I293" s="259"/>
       <c r="J293" s="88"/>
       <c r="K293" s="1"/>
       <c r="L293" s="73"/>
@@ -13714,11 +13714,11 @@
       </c>
       <c r="E294" s="71"/>
       <c r="F294" s="1"/>
-      <c r="G294" s="257" t="s">
+      <c r="G294" s="262" t="s">
         <v>55</v>
       </c>
       <c r="H294" s="158"/>
-      <c r="I294" s="255">
+      <c r="I294" s="260">
         <f>SUM(I289:J293)</f>
         <v>0</v>
       </c>
@@ -13742,7 +13742,7 @@
     </row>
     <row r="295" spans="1:26" ht="18.75" customHeight="1">
       <c r="A295" s="74"/>
-      <c r="B295" s="258" t="s">
+      <c r="B295" s="263" t="s">
         <v>55</v>
       </c>
       <c r="C295" s="162"/>
@@ -13860,7 +13860,7 @@
       <c r="Z298" s="1"/>
     </row>
     <row r="299" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A299" s="290" t="s">
+      <c r="A299" s="295" t="s">
         <v>67</v>
       </c>
       <c r="B299" s="114"/>
@@ -13868,15 +13868,15 @@
       <c r="D299" s="114"/>
       <c r="E299" s="114"/>
       <c r="F299" s="114"/>
-      <c r="G299" s="212"/>
+      <c r="G299" s="218"/>
       <c r="H299" s="78" t="s">
         <v>138</v>
       </c>
-      <c r="I299" s="259" t="s">
+      <c r="I299" s="264" t="s">
         <v>139</v>
       </c>
-      <c r="J299" s="212"/>
-      <c r="K299" s="260" t="s">
+      <c r="J299" s="218"/>
+      <c r="K299" s="265" t="s">
         <v>140</v>
       </c>
       <c r="L299" s="115"/>
@@ -13896,7 +13896,7 @@
       <c r="Z299" s="1"/>
     </row>
     <row r="300" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A300" s="252" t="s">
+      <c r="A300" s="257" t="s">
         <v>141</v>
       </c>
       <c r="B300" s="87"/>
@@ -13906,9 +13906,9 @@
       <c r="F300" s="87"/>
       <c r="G300" s="91"/>
       <c r="H300" s="79"/>
-      <c r="I300" s="253"/>
+      <c r="I300" s="258"/>
       <c r="J300" s="91"/>
-      <c r="K300" s="261">
+      <c r="K300" s="266">
         <f t="shared" ref="K300:K331" si="2">H300*I300</f>
         <v>0</v>
       </c>
@@ -13929,7 +13929,7 @@
       <c r="Z300" s="1"/>
     </row>
     <row r="301" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A301" s="252" t="s">
+      <c r="A301" s="257" t="s">
         <v>141</v>
       </c>
       <c r="B301" s="87"/>
@@ -13939,9 +13939,9 @@
       <c r="F301" s="87"/>
       <c r="G301" s="91"/>
       <c r="H301" s="79"/>
-      <c r="I301" s="253"/>
+      <c r="I301" s="258"/>
       <c r="J301" s="91"/>
-      <c r="K301" s="261">
+      <c r="K301" s="266">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -13962,7 +13962,7 @@
       <c r="Z301" s="1"/>
     </row>
     <row r="302" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A302" s="252" t="s">
+      <c r="A302" s="257" t="s">
         <v>141</v>
       </c>
       <c r="B302" s="87"/>
@@ -13972,9 +13972,9 @@
       <c r="F302" s="87"/>
       <c r="G302" s="91"/>
       <c r="H302" s="79"/>
-      <c r="I302" s="253"/>
+      <c r="I302" s="258"/>
       <c r="J302" s="91"/>
-      <c r="K302" s="261">
+      <c r="K302" s="266">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -13995,7 +13995,7 @@
       <c r="Z302" s="1"/>
     </row>
     <row r="303" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A303" s="252" t="s">
+      <c r="A303" s="257" t="s">
         <v>141</v>
       </c>
       <c r="B303" s="87"/>
@@ -14005,9 +14005,9 @@
       <c r="F303" s="87"/>
       <c r="G303" s="91"/>
       <c r="H303" s="79"/>
-      <c r="I303" s="253"/>
+      <c r="I303" s="258"/>
       <c r="J303" s="91"/>
-      <c r="K303" s="261">
+      <c r="K303" s="266">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -14028,7 +14028,7 @@
       <c r="Z303" s="1"/>
     </row>
     <row r="304" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A304" s="252" t="s">
+      <c r="A304" s="257" t="s">
         <v>141</v>
       </c>
       <c r="B304" s="87"/>
@@ -14038,9 +14038,9 @@
       <c r="F304" s="87"/>
       <c r="G304" s="91"/>
       <c r="H304" s="79"/>
-      <c r="I304" s="253"/>
+      <c r="I304" s="258"/>
       <c r="J304" s="91"/>
-      <c r="K304" s="261">
+      <c r="K304" s="266">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -14061,7 +14061,7 @@
       <c r="Z304" s="1"/>
     </row>
     <row r="305" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A305" s="252" t="s">
+      <c r="A305" s="257" t="s">
         <v>141</v>
       </c>
       <c r="B305" s="87"/>
@@ -14071,9 +14071,9 @@
       <c r="F305" s="87"/>
       <c r="G305" s="91"/>
       <c r="H305" s="79"/>
-      <c r="I305" s="253"/>
+      <c r="I305" s="258"/>
       <c r="J305" s="91"/>
-      <c r="K305" s="261">
+      <c r="K305" s="266">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -14094,7 +14094,7 @@
       <c r="Z305" s="1"/>
     </row>
     <row r="306" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A306" s="252" t="s">
+      <c r="A306" s="257" t="s">
         <v>141</v>
       </c>
       <c r="B306" s="87"/>
@@ -14104,9 +14104,9 @@
       <c r="F306" s="87"/>
       <c r="G306" s="91"/>
       <c r="H306" s="79"/>
-      <c r="I306" s="253"/>
+      <c r="I306" s="258"/>
       <c r="J306" s="91"/>
-      <c r="K306" s="261">
+      <c r="K306" s="266">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -14127,7 +14127,7 @@
       <c r="Z306" s="1"/>
     </row>
     <row r="307" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A307" s="252" t="s">
+      <c r="A307" s="257" t="s">
         <v>141</v>
       </c>
       <c r="B307" s="87"/>
@@ -14137,9 +14137,9 @@
       <c r="F307" s="87"/>
       <c r="G307" s="91"/>
       <c r="H307" s="79"/>
-      <c r="I307" s="253"/>
+      <c r="I307" s="258"/>
       <c r="J307" s="91"/>
-      <c r="K307" s="261">
+      <c r="K307" s="266">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -14160,7 +14160,7 @@
       <c r="Z307" s="1"/>
     </row>
     <row r="308" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A308" s="252" t="s">
+      <c r="A308" s="257" t="s">
         <v>141</v>
       </c>
       <c r="B308" s="87"/>
@@ -14170,9 +14170,9 @@
       <c r="F308" s="87"/>
       <c r="G308" s="91"/>
       <c r="H308" s="79"/>
-      <c r="I308" s="253"/>
+      <c r="I308" s="258"/>
       <c r="J308" s="91"/>
-      <c r="K308" s="261">
+      <c r="K308" s="266">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -14193,7 +14193,7 @@
       <c r="Z308" s="1"/>
     </row>
     <row r="309" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A309" s="252" t="s">
+      <c r="A309" s="257" t="s">
         <v>141</v>
       </c>
       <c r="B309" s="87"/>
@@ -14203,9 +14203,9 @@
       <c r="F309" s="87"/>
       <c r="G309" s="91"/>
       <c r="H309" s="79"/>
-      <c r="I309" s="253"/>
+      <c r="I309" s="258"/>
       <c r="J309" s="91"/>
-      <c r="K309" s="261">
+      <c r="K309" s="266">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -14226,7 +14226,7 @@
       <c r="Z309" s="1"/>
     </row>
     <row r="310" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A310" s="252" t="s">
+      <c r="A310" s="257" t="s">
         <v>141</v>
       </c>
       <c r="B310" s="87"/>
@@ -14236,9 +14236,9 @@
       <c r="F310" s="87"/>
       <c r="G310" s="91"/>
       <c r="H310" s="79"/>
-      <c r="I310" s="253"/>
+      <c r="I310" s="258"/>
       <c r="J310" s="91"/>
-      <c r="K310" s="261">
+      <c r="K310" s="266">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -14259,7 +14259,7 @@
       <c r="Z310" s="1"/>
     </row>
     <row r="311" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A311" s="252" t="s">
+      <c r="A311" s="257" t="s">
         <v>141</v>
       </c>
       <c r="B311" s="87"/>
@@ -14269,9 +14269,9 @@
       <c r="F311" s="87"/>
       <c r="G311" s="91"/>
       <c r="H311" s="79"/>
-      <c r="I311" s="253"/>
+      <c r="I311" s="258"/>
       <c r="J311" s="91"/>
-      <c r="K311" s="261">
+      <c r="K311" s="266">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -14292,7 +14292,7 @@
       <c r="Z311" s="1"/>
     </row>
     <row r="312" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A312" s="252" t="s">
+      <c r="A312" s="257" t="s">
         <v>141</v>
       </c>
       <c r="B312" s="87"/>
@@ -14302,9 +14302,9 @@
       <c r="F312" s="87"/>
       <c r="G312" s="91"/>
       <c r="H312" s="79"/>
-      <c r="I312" s="253"/>
+      <c r="I312" s="258"/>
       <c r="J312" s="91"/>
-      <c r="K312" s="261">
+      <c r="K312" s="266">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -14325,7 +14325,7 @@
       <c r="Z312" s="1"/>
     </row>
     <row r="313" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A313" s="252" t="s">
+      <c r="A313" s="257" t="s">
         <v>141</v>
       </c>
       <c r="B313" s="87"/>
@@ -14335,9 +14335,9 @@
       <c r="F313" s="87"/>
       <c r="G313" s="91"/>
       <c r="H313" s="79"/>
-      <c r="I313" s="253"/>
+      <c r="I313" s="258"/>
       <c r="J313" s="91"/>
-      <c r="K313" s="261">
+      <c r="K313" s="266">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -14358,7 +14358,7 @@
       <c r="Z313" s="1"/>
     </row>
     <row r="314" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A314" s="252" t="s">
+      <c r="A314" s="257" t="s">
         <v>141</v>
       </c>
       <c r="B314" s="87"/>
@@ -14368,9 +14368,9 @@
       <c r="F314" s="87"/>
       <c r="G314" s="91"/>
       <c r="H314" s="79"/>
-      <c r="I314" s="253"/>
+      <c r="I314" s="258"/>
       <c r="J314" s="91"/>
-      <c r="K314" s="261">
+      <c r="K314" s="266">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -14391,7 +14391,7 @@
       <c r="Z314" s="1"/>
     </row>
     <row r="315" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A315" s="252" t="s">
+      <c r="A315" s="257" t="s">
         <v>141</v>
       </c>
       <c r="B315" s="87"/>
@@ -14401,9 +14401,9 @@
       <c r="F315" s="87"/>
       <c r="G315" s="91"/>
       <c r="H315" s="79"/>
-      <c r="I315" s="253"/>
+      <c r="I315" s="258"/>
       <c r="J315" s="91"/>
-      <c r="K315" s="261">
+      <c r="K315" s="266">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -14424,7 +14424,7 @@
       <c r="Z315" s="1"/>
     </row>
     <row r="316" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A316" s="252" t="s">
+      <c r="A316" s="257" t="s">
         <v>141</v>
       </c>
       <c r="B316" s="87"/>
@@ -14434,9 +14434,9 @@
       <c r="F316" s="87"/>
       <c r="G316" s="91"/>
       <c r="H316" s="79"/>
-      <c r="I316" s="253"/>
+      <c r="I316" s="258"/>
       <c r="J316" s="91"/>
-      <c r="K316" s="261">
+      <c r="K316" s="266">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -14457,7 +14457,7 @@
       <c r="Z316" s="1"/>
     </row>
     <row r="317" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A317" s="252" t="s">
+      <c r="A317" s="257" t="s">
         <v>141</v>
       </c>
       <c r="B317" s="87"/>
@@ -14467,9 +14467,9 @@
       <c r="F317" s="87"/>
       <c r="G317" s="91"/>
       <c r="H317" s="79"/>
-      <c r="I317" s="253"/>
+      <c r="I317" s="258"/>
       <c r="J317" s="91"/>
-      <c r="K317" s="261">
+      <c r="K317" s="266">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -14490,7 +14490,7 @@
       <c r="Z317" s="1"/>
     </row>
     <row r="318" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A318" s="252" t="s">
+      <c r="A318" s="257" t="s">
         <v>141</v>
       </c>
       <c r="B318" s="87"/>
@@ -14500,9 +14500,9 @@
       <c r="F318" s="87"/>
       <c r="G318" s="91"/>
       <c r="H318" s="79"/>
-      <c r="I318" s="253"/>
+      <c r="I318" s="258"/>
       <c r="J318" s="91"/>
-      <c r="K318" s="261">
+      <c r="K318" s="266">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -14523,7 +14523,7 @@
       <c r="Z318" s="1"/>
     </row>
     <row r="319" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A319" s="252" t="s">
+      <c r="A319" s="257" t="s">
         <v>141</v>
       </c>
       <c r="B319" s="87"/>
@@ -14533,9 +14533,9 @@
       <c r="F319" s="87"/>
       <c r="G319" s="91"/>
       <c r="H319" s="79"/>
-      <c r="I319" s="253"/>
+      <c r="I319" s="258"/>
       <c r="J319" s="91"/>
-      <c r="K319" s="261">
+      <c r="K319" s="266">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -14556,7 +14556,7 @@
       <c r="Z319" s="1"/>
     </row>
     <row r="320" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A320" s="252" t="s">
+      <c r="A320" s="257" t="s">
         <v>141</v>
       </c>
       <c r="B320" s="87"/>
@@ -14566,9 +14566,9 @@
       <c r="F320" s="87"/>
       <c r="G320" s="91"/>
       <c r="H320" s="79"/>
-      <c r="I320" s="253"/>
+      <c r="I320" s="258"/>
       <c r="J320" s="91"/>
-      <c r="K320" s="261">
+      <c r="K320" s="266">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -14589,7 +14589,7 @@
       <c r="Z320" s="1"/>
     </row>
     <row r="321" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A321" s="252" t="s">
+      <c r="A321" s="257" t="s">
         <v>141</v>
       </c>
       <c r="B321" s="87"/>
@@ -14599,9 +14599,9 @@
       <c r="F321" s="87"/>
       <c r="G321" s="91"/>
       <c r="H321" s="79"/>
-      <c r="I321" s="253"/>
+      <c r="I321" s="258"/>
       <c r="J321" s="91"/>
-      <c r="K321" s="261">
+      <c r="K321" s="266">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -14622,7 +14622,7 @@
       <c r="Z321" s="1"/>
     </row>
     <row r="322" spans="1:26" ht="18" customHeight="1">
-      <c r="A322" s="252" t="s">
+      <c r="A322" s="257" t="s">
         <v>141</v>
       </c>
       <c r="B322" s="87"/>
@@ -14632,9 +14632,9 @@
       <c r="F322" s="87"/>
       <c r="G322" s="91"/>
       <c r="H322" s="79"/>
-      <c r="I322" s="253"/>
+      <c r="I322" s="258"/>
       <c r="J322" s="91"/>
-      <c r="K322" s="261">
+      <c r="K322" s="266">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -14655,7 +14655,7 @@
       <c r="Z322" s="1"/>
     </row>
     <row r="323" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A323" s="252" t="s">
+      <c r="A323" s="257" t="s">
         <v>141</v>
       </c>
       <c r="B323" s="87"/>
@@ -14665,9 +14665,9 @@
       <c r="F323" s="87"/>
       <c r="G323" s="91"/>
       <c r="H323" s="79"/>
-      <c r="I323" s="253"/>
+      <c r="I323" s="258"/>
       <c r="J323" s="91"/>
-      <c r="K323" s="261">
+      <c r="K323" s="266">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -14688,7 +14688,7 @@
       <c r="Z323" s="1"/>
     </row>
     <row r="324" spans="1:26" ht="18" customHeight="1">
-      <c r="A324" s="252" t="s">
+      <c r="A324" s="257" t="s">
         <v>141</v>
       </c>
       <c r="B324" s="87"/>
@@ -14698,9 +14698,9 @@
       <c r="F324" s="87"/>
       <c r="G324" s="91"/>
       <c r="H324" s="79"/>
-      <c r="I324" s="253"/>
+      <c r="I324" s="258"/>
       <c r="J324" s="91"/>
-      <c r="K324" s="261">
+      <c r="K324" s="266">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -14721,7 +14721,7 @@
       <c r="Z324" s="1"/>
     </row>
     <row r="325" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A325" s="252" t="s">
+      <c r="A325" s="257" t="s">
         <v>141</v>
       </c>
       <c r="B325" s="87"/>
@@ -14731,9 +14731,9 @@
       <c r="F325" s="87"/>
       <c r="G325" s="91"/>
       <c r="H325" s="79"/>
-      <c r="I325" s="253"/>
+      <c r="I325" s="258"/>
       <c r="J325" s="91"/>
-      <c r="K325" s="261">
+      <c r="K325" s="266">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -14754,7 +14754,7 @@
       <c r="Z325" s="1"/>
     </row>
     <row r="326" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A326" s="252" t="s">
+      <c r="A326" s="257" t="s">
         <v>141</v>
       </c>
       <c r="B326" s="87"/>
@@ -14764,9 +14764,9 @@
       <c r="F326" s="87"/>
       <c r="G326" s="91"/>
       <c r="H326" s="79"/>
-      <c r="I326" s="253"/>
+      <c r="I326" s="258"/>
       <c r="J326" s="91"/>
-      <c r="K326" s="261">
+      <c r="K326" s="266">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -14787,7 +14787,7 @@
       <c r="Z326" s="1"/>
     </row>
     <row r="327" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A327" s="252" t="s">
+      <c r="A327" s="257" t="s">
         <v>141</v>
       </c>
       <c r="B327" s="87"/>
@@ -14797,9 +14797,9 @@
       <c r="F327" s="87"/>
       <c r="G327" s="91"/>
       <c r="H327" s="79"/>
-      <c r="I327" s="253"/>
+      <c r="I327" s="258"/>
       <c r="J327" s="91"/>
-      <c r="K327" s="261">
+      <c r="K327" s="266">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -14820,7 +14820,7 @@
       <c r="Z327" s="1"/>
     </row>
     <row r="328" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A328" s="252" t="s">
+      <c r="A328" s="257" t="s">
         <v>141</v>
       </c>
       <c r="B328" s="87"/>
@@ -14830,9 +14830,9 @@
       <c r="F328" s="87"/>
       <c r="G328" s="91"/>
       <c r="H328" s="79"/>
-      <c r="I328" s="253"/>
+      <c r="I328" s="258"/>
       <c r="J328" s="91"/>
-      <c r="K328" s="261">
+      <c r="K328" s="266">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -14853,7 +14853,7 @@
       <c r="Z328" s="1"/>
     </row>
     <row r="329" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A329" s="252" t="s">
+      <c r="A329" s="257" t="s">
         <v>141</v>
       </c>
       <c r="B329" s="87"/>
@@ -14863,9 +14863,9 @@
       <c r="F329" s="87"/>
       <c r="G329" s="91"/>
       <c r="H329" s="79"/>
-      <c r="I329" s="253"/>
+      <c r="I329" s="258"/>
       <c r="J329" s="91"/>
-      <c r="K329" s="261">
+      <c r="K329" s="266">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -14886,7 +14886,7 @@
       <c r="Z329" s="1"/>
     </row>
     <row r="330" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A330" s="252" t="s">
+      <c r="A330" s="257" t="s">
         <v>141</v>
       </c>
       <c r="B330" s="87"/>
@@ -14896,9 +14896,9 @@
       <c r="F330" s="87"/>
       <c r="G330" s="91"/>
       <c r="H330" s="79"/>
-      <c r="I330" s="253"/>
+      <c r="I330" s="258"/>
       <c r="J330" s="91"/>
-      <c r="K330" s="261">
+      <c r="K330" s="266">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -14919,7 +14919,7 @@
       <c r="Z330" s="1"/>
     </row>
     <row r="331" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A331" s="252" t="s">
+      <c r="A331" s="257" t="s">
         <v>141</v>
       </c>
       <c r="B331" s="87"/>
@@ -14929,9 +14929,9 @@
       <c r="F331" s="87"/>
       <c r="G331" s="91"/>
       <c r="H331" s="79"/>
-      <c r="I331" s="253"/>
+      <c r="I331" s="258"/>
       <c r="J331" s="91"/>
-      <c r="K331" s="261">
+      <c r="K331" s="266">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -14952,7 +14952,7 @@
       <c r="Z331" s="1"/>
     </row>
     <row r="332" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A332" s="298" t="s">
+      <c r="A332" s="303" t="s">
         <v>55</v>
       </c>
       <c r="B332" s="162"/>
@@ -14964,7 +14964,7 @@
       <c r="H332" s="162"/>
       <c r="I332" s="162"/>
       <c r="J332" s="158"/>
-      <c r="K332" s="292">
+      <c r="K332" s="297">
         <f>SUM(K300:L331)</f>
         <v>0</v>
       </c>
@@ -15013,7 +15013,7 @@
       <c r="Z333" s="1"/>
     </row>
     <row r="334" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A334" s="293" t="s">
+      <c r="A334" s="298" t="s">
         <v>142</v>
       </c>
       <c r="B334" s="117"/>
@@ -15043,7 +15043,7 @@
       <c r="Z334" s="1"/>
     </row>
     <row r="335" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A335" s="294" t="s">
+      <c r="A335" s="299" t="s">
         <v>143</v>
       </c>
       <c r="B335" s="114"/>
@@ -15073,21 +15073,21 @@
       <c r="Z335" s="1"/>
     </row>
     <row r="336" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A336" s="295" t="s">
+      <c r="A336" s="300" t="s">
         <v>144</v>
       </c>
       <c r="B336" s="87"/>
       <c r="C336" s="87"/>
       <c r="D336" s="91"/>
-      <c r="E336" s="296" t="s">
+      <c r="E336" s="301" t="s">
         <v>145</v>
       </c>
       <c r="F336" s="91"/>
-      <c r="G336" s="297" t="s">
+      <c r="G336" s="302" t="s">
         <v>146</v>
       </c>
       <c r="H336" s="91"/>
-      <c r="I336" s="297" t="s">
+      <c r="I336" s="302" t="s">
         <v>147</v>
       </c>
       <c r="J336" s="87"/>
@@ -15109,7 +15109,7 @@
       <c r="Z336" s="1"/>
     </row>
     <row r="337" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A337" s="291"/>
+      <c r="A337" s="296"/>
       <c r="B337" s="87"/>
       <c r="C337" s="87"/>
       <c r="D337" s="91"/>
@@ -15139,7 +15139,7 @@
       <c r="Z337" s="1"/>
     </row>
     <row r="338" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A338" s="291"/>
+      <c r="A338" s="296"/>
       <c r="B338" s="87"/>
       <c r="C338" s="87"/>
       <c r="D338" s="91"/>
@@ -15169,7 +15169,7 @@
       <c r="Z338" s="1"/>
     </row>
     <row r="339" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A339" s="291"/>
+      <c r="A339" s="296"/>
       <c r="B339" s="87"/>
       <c r="C339" s="87"/>
       <c r="D339" s="91"/>
@@ -15199,7 +15199,7 @@
       <c r="Z339" s="1"/>
     </row>
     <row r="340" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A340" s="291"/>
+      <c r="A340" s="296"/>
       <c r="B340" s="87"/>
       <c r="C340" s="87"/>
       <c r="D340" s="91"/>
@@ -15229,7 +15229,7 @@
       <c r="Z340" s="1"/>
     </row>
     <row r="341" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A341" s="291"/>
+      <c r="A341" s="296"/>
       <c r="B341" s="87"/>
       <c r="C341" s="87"/>
       <c r="D341" s="91"/>
@@ -15259,7 +15259,7 @@
       <c r="Z341" s="1"/>
     </row>
     <row r="342" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A342" s="291"/>
+      <c r="A342" s="296"/>
       <c r="B342" s="87"/>
       <c r="C342" s="87"/>
       <c r="D342" s="91"/>
@@ -15289,15 +15289,15 @@
       <c r="Z342" s="1"/>
     </row>
     <row r="343" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A343" s="299"/>
+      <c r="A343" s="304"/>
       <c r="B343" s="162"/>
       <c r="C343" s="162"/>
       <c r="D343" s="158"/>
-      <c r="E343" s="262"/>
+      <c r="E343" s="267"/>
       <c r="F343" s="158"/>
-      <c r="G343" s="262"/>
+      <c r="G343" s="267"/>
       <c r="H343" s="158"/>
-      <c r="I343" s="263" t="s">
+      <c r="I343" s="268" t="s">
         <v>148</v>
       </c>
       <c r="J343" s="162"/>
